--- a/public/tests/data/test_rb.xlsx
+++ b/public/tests/data/test_rb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D66FDE7-A9E5-4FD4-8423-BAAF63AC6D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B62A5BF-3984-4994-927C-750D12FAF632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>Name</t>
   </si>
@@ -177,15 +177,19 @@
   </si>
   <si>
     <t>monthly</t>
+  </si>
+  <si>
+    <t>_WD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="0.0000%"/>
+    <numFmt numFmtId="173" formatCode="[$]dddd" x16r2:formatCode16="[$-en-SE]dddd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -232,7 +236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -246,6 +250,12 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1341,14 +1351,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.4609375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -1367,8 +1378,11 @@
       <c r="F1" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1387,8 +1401,11 @@
       <c r="F2" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
@@ -1407,8 +1424,12 @@
       <c r="F3" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G3" s="13">
+        <f>A3</f>
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
@@ -1428,8 +1449,12 @@
         <f xml:space="preserve"> $D4 * Prices!$D3 + $E4 * Prices!$E3</f>
         <v>0.95500000000000007</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G4" s="13">
+        <f>A4</f>
+        <v>45659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
@@ -1451,8 +1476,12 @@
         <f xml:space="preserve"> $D5 * Prices!$D4 + $E5 * Prices!$E4</f>
         <v>1.0575916230366491</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G5" s="13">
+        <f>A5</f>
+        <v>45660</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
@@ -1474,8 +1503,12 @@
         <f xml:space="preserve"> $D6 * Prices!$D5 + $E6 * Prices!$E5</f>
         <v>0.95544554455445552</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G6" s="13">
+        <f>A6</f>
+        <v>45661</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
@@ -1497,8 +1530,12 @@
         <f xml:space="preserve"> $D7 * Prices!$D6 + $E7 * Prices!$E6</f>
         <v>1.0569948186528499</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G7" s="13">
+        <f>A7</f>
+        <v>45662</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
@@ -1518,8 +1555,12 @@
         <f xml:space="preserve"> $D8 * Prices!$D7 + $E8 * Prices!$E7</f>
         <v>0.95480769230769225</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G8" s="14">
+        <f>A8</f>
+        <v>45663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
@@ -1541,8 +1582,12 @@
         <f xml:space="preserve"> $D9 * Prices!$D8 + $E9 * Prices!$E8</f>
         <v>1.0574018126888218</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G9" s="13">
+        <f>A9</f>
+        <v>45664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
@@ -1564,8 +1609,12 @@
         <f xml:space="preserve"> $D10 * Prices!$D9 + $E10 * Prices!$E9</f>
         <v>0.95523809523809522</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G10" s="13">
+        <f>A10</f>
+        <v>45665</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
@@ -1587,8 +1636,12 @@
         <f xml:space="preserve"> $D11 * Prices!$D10 + $E11 * Prices!$E10</f>
         <v>1.0568295114656032</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G11" s="13">
+        <f>A11</f>
+        <v>45666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
@@ -1610,8 +1663,12 @@
         <f xml:space="preserve"> $D12 * Prices!$D11 + $E12 * Prices!$E11</f>
         <v>0.95566037735849063</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G12" s="13">
+        <f>A12</f>
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
@@ -1633,8 +1690,12 @@
         <f xml:space="preserve"> $D13 * Prices!$D12 + $E13 * Prices!$E12</f>
         <v>1.0562685093780848</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G13" s="13">
+        <f>A13</f>
+        <v>45668</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
@@ -1656,8 +1717,12 @@
         <f xml:space="preserve"> $D14 * Prices!$D13 + $E14 * Prices!$E13</f>
         <v>0.9560747663551401</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G14" s="13">
+        <f>A14</f>
+        <v>45669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
@@ -1677,8 +1742,12 @@
         <f xml:space="preserve"> $D15 * Prices!$D14 + $E15 * Prices!$E14</f>
         <v>1.06006006006006</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G15" s="14">
+        <f>A15</f>
+        <v>45670</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
@@ -1700,8 +1769,12 @@
         <f xml:space="preserve"> $D16 * Prices!$D15 + $E16 * Prices!$E15</f>
         <v>0.95184135977337103</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G16" s="13">
+        <f>A16</f>
+        <v>45671</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
@@ -1723,8 +1796,12 @@
         <f xml:space="preserve"> $D17 * Prices!$D16 + $E17 * Prices!$E16</f>
         <v>1.0595238095238098</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G17" s="13">
+        <f>A17</f>
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
@@ -1746,8 +1823,12 @@
         <f xml:space="preserve"> $D18 * Prices!$D17 + $E18 * Prices!$E17</f>
         <v>0.95224719101123578</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G18" s="13">
+        <f>A18</f>
+        <v>45673</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
@@ -1769,8 +1850,12 @@
         <f xml:space="preserve"> $D19 * Prices!$D18 + $E19 * Prices!$E18</f>
         <v>1.0589970501474928</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G19" s="13">
+        <f>A19</f>
+        <v>45674</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
@@ -1792,8 +1877,12 @@
         <f xml:space="preserve"> $D20 * Prices!$D19 + $E20 * Prices!$E19</f>
         <v>0.9526462395543176</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G20" s="13">
+        <f>A20</f>
+        <v>45675</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
@@ -1815,8 +1904,12 @@
         <f xml:space="preserve"> $D21 * Prices!$D20 + $E21 * Prices!$E20</f>
         <v>1.0584795321637426</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G21" s="13">
+        <f>A21</f>
+        <v>45676</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
@@ -1836,8 +1929,12 @@
         <f xml:space="preserve"> $D22 * Prices!$D21 + $E22 * Prices!$E21</f>
         <v>0.95423728813559316</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G22" s="14">
+        <f>A22</f>
+        <v>45677</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
@@ -1859,8 +1956,12 @@
         <f xml:space="preserve"> $D23 * Prices!$D22 + $E23 * Prices!$E22</f>
         <v>1.0568383658969807</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G23" s="13">
+        <f>A23</f>
+        <v>45678</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
@@ -1882,8 +1983,12 @@
         <f xml:space="preserve"> $D24 * Prices!$D23 + $E24 * Prices!$E23</f>
         <v>0.95462184873949563</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G24" s="13">
+        <f>A24</f>
+        <v>45679</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
@@ -1905,8 +2010,12 @@
         <f xml:space="preserve"> $D25 * Prices!$D24 + $E25 * Prices!$E24</f>
         <v>1.0563380281690142</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G25" s="13">
+        <f>A25</f>
+        <v>45680</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
@@ -1928,8 +2037,12 @@
         <f xml:space="preserve"> $D26 * Prices!$D25 + $E26 * Prices!$E25</f>
         <v>0.95500000000000007</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G26" s="13">
+        <f>A26</f>
+        <v>45681</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
@@ -1951,8 +2064,12 @@
         <f xml:space="preserve"> $D27 * Prices!$D26 + $E27 * Prices!$E26</f>
         <v>1.0558464223385688</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G27" s="13">
+        <f>A27</f>
+        <v>45682</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
@@ -1974,8 +2091,12 @@
         <f xml:space="preserve"> $D28 * Prices!$D27 + $E28 * Prices!$E27</f>
         <v>0.95537190082644619</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G28" s="13">
+        <f>A28</f>
+        <v>45683</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
@@ -1995,8 +2116,12 @@
         <f xml:space="preserve"> $D29 * Prices!$D28 + $E29 * Prices!$E28</f>
         <v>1.0595555555555556</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G29" s="14">
+        <f>A29</f>
+        <v>45684</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
@@ -2018,8 +2143,12 @@
         <f xml:space="preserve"> $D30 * Prices!$D29 + $E30 * Prices!$E29</f>
         <v>0.95134228187919456</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G30" s="13">
+        <f>A30</f>
+        <v>45685</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
@@ -2041,8 +2170,12 @@
         <f xml:space="preserve"> $D31 * Prices!$D30 + $E31 * Prices!$E30</f>
         <v>1.0590828924162259</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G31" s="13">
+        <f>A31</f>
+        <v>45686</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
@@ -2064,8 +2197,12 @@
         <f xml:space="preserve"> $D32 * Prices!$D31 + $E32 * Prices!$E31</f>
         <v>0.95170691090757686</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G32" s="13">
+        <f>A32</f>
+        <v>45687</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
@@ -2087,8 +2224,12 @@
         <f xml:space="preserve"> $D33 * Prices!$D32 + $E33 * Prices!$E32</f>
         <v>1.0586176727909011</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G33" s="13">
+        <f>A33</f>
+        <v>45688</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>45689</v>
       </c>
@@ -2109,6 +2250,10 @@
       <c r="F34" s="8">
         <f xml:space="preserve"> $D34 * Prices!$D33 + $E34 * Prices!$E33</f>
         <v>0.95206611570247945</v>
+      </c>
+      <c r="G34" s="13">
+        <f>A34</f>
+        <v>45689</v>
       </c>
     </row>
   </sheetData>
@@ -2781,13 +2926,13 @@
         <v>31</v>
       </c>
       <c r="F4" s="5">
-        <v>10.5</v>
+        <v>9.42</v>
       </c>
       <c r="G4" s="5">
-        <v>224.27</v>
+        <v>188.72</v>
       </c>
       <c r="H4" s="5">
-        <v>75.599999999999994</v>
+        <v>82.08</v>
       </c>
       <c r="I4" s="5">
         <v>1.4</v>

--- a/public/tests/data/test_rb.xlsx
+++ b/public/tests/data/test_rb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B62A5BF-3984-4994-927C-750D12FAF632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484F7D5-D0AE-4C5D-94F8-A32F13F9AB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1355,905 +1355,905 @@
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.15234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.4609375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>16</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
-      <c r="B3" s="6">
-        <v>1</v>
+      <c r="B3" s="13">
+        <f>A3</f>
+        <v>45658</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
       </c>
-      <c r="D3" s="11">
-        <v>0.5</v>
+      <c r="D3" s="6">
+        <v>1</v>
       </c>
       <c r="E3" s="11">
         <v>0.5</v>
       </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="13">
-        <f>A3</f>
-        <v>45658</v>
+      <c r="F3" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
-      <c r="B4" s="6">
-        <v>1</v>
+      <c r="B4" s="13">
+        <f>A4</f>
+        <v>45659</v>
       </c>
       <c r="C4" s="6">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
-        <v>0.5</v>
+      <c r="D4" s="6">
+        <v>1</v>
       </c>
       <c r="E4" s="11">
         <v>0.5</v>
       </c>
-      <c r="F4" s="8">
-        <f xml:space="preserve"> $D4 * Prices!$D3 + $E4 * Prices!$E3</f>
+      <c r="F4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="8">
+        <f xml:space="preserve"> $E4 * Prices!$D3 + $F4 * Prices!$E3</f>
         <v>0.95500000000000007</v>
-      </c>
-      <c r="G4" s="13">
-        <f>A4</f>
-        <v>45659</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
-      <c r="B5" s="6">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="11">
-        <f>(D4 * Prices!D3) / $F4</f>
-        <v>0.52879581151832455</v>
-      </c>
-      <c r="E5" s="11">
-        <f>(E4 * Prices!E3) / $F4</f>
-        <v>0.47120418848167539</v>
-      </c>
-      <c r="F5" s="8">
-        <f xml:space="preserve"> $D5 * Prices!$D4 + $E5 * Prices!$E4</f>
-        <v>1.0575916230366491</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="B5" s="13">
         <f>A5</f>
         <v>45660</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
+        <f>(E4 * Prices!D3) / $G4</f>
+        <v>0.52879581151832455</v>
+      </c>
+      <c r="F5" s="11">
+        <f>(F4 * Prices!E3) / $G4</f>
+        <v>0.47120418848167539</v>
+      </c>
+      <c r="G5" s="8">
+        <f xml:space="preserve"> $E5 * Prices!$D4 + $F5 * Prices!$E4</f>
+        <v>1.0575916230366491</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="11">
-        <f>(D5 * Prices!D4) / $F5</f>
-        <v>0.50495049504950495</v>
-      </c>
-      <c r="E6" s="11">
-        <f>(E5 * Prices!E4) / F5</f>
-        <v>0.4950495049504951</v>
-      </c>
-      <c r="F6" s="8">
-        <f xml:space="preserve"> $D6 * Prices!$D5 + $E6 * Prices!$E5</f>
-        <v>0.95544554455445552</v>
-      </c>
-      <c r="G6" s="13">
+      <c r="B6" s="13">
         <f>A6</f>
         <v>45661</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
+        <f>(E5 * Prices!D4) / $G5</f>
+        <v>0.50495049504950495</v>
+      </c>
+      <c r="F6" s="11">
+        <f>(F5 * Prices!E4) / G5</f>
+        <v>0.4950495049504951</v>
+      </c>
+      <c r="G6" s="8">
+        <f xml:space="preserve"> $E6 * Prices!$D5 + $F6 * Prices!$E5</f>
+        <v>0.95544554455445552</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11">
-        <f>(D6 * Prices!D5) / $F6</f>
-        <v>0.53367875647668395</v>
-      </c>
-      <c r="E7" s="11">
-        <f>(E6 * Prices!E5) / F6</f>
-        <v>0.46632124352331611</v>
-      </c>
-      <c r="F7" s="8">
-        <f xml:space="preserve"> $D7 * Prices!$D6 + $E7 * Prices!$E6</f>
-        <v>1.0569948186528499</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="B7" s="13">
         <f>A7</f>
         <v>45662</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11">
+        <f>(E6 * Prices!D5) / $G6</f>
+        <v>0.53367875647668395</v>
+      </c>
+      <c r="F7" s="11">
+        <f>(F6 * Prices!E5) / G6</f>
+        <v>0.46632124352331611</v>
+      </c>
+      <c r="G7" s="8">
+        <f xml:space="preserve"> $E7 * Prices!$D6 + $F7 * Prices!$E6</f>
+        <v>1.0569948186528499</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
-      <c r="B8" s="6">
-        <v>1</v>
+      <c r="B8" s="14">
+        <f>A8</f>
+        <v>45663</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
       </c>
-      <c r="D8" s="10">
-        <v>0.5</v>
+      <c r="D8" s="6">
+        <v>1</v>
       </c>
       <c r="E8" s="10">
         <v>0.5</v>
       </c>
-      <c r="F8" s="8">
-        <f xml:space="preserve"> $D8 * Prices!$D7 + $E8 * Prices!$E7</f>
+      <c r="F8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="8">
+        <f xml:space="preserve"> $E8 * Prices!$D7 + $F8 * Prices!$E7</f>
         <v>0.95480769230769225</v>
-      </c>
-      <c r="G8" s="14">
-        <f>A8</f>
-        <v>45663</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
-      <c r="B9" s="6">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11">
-        <f>(D8 * Prices!D7) / $F8</f>
-        <v>0.52870090634441091</v>
-      </c>
-      <c r="E9" s="11">
-        <f>(E8 * Prices!E7) / F8</f>
-        <v>0.47129909365558914</v>
-      </c>
-      <c r="F9" s="8">
-        <f xml:space="preserve"> $D9 * Prices!$D8 + $E9 * Prices!$E8</f>
-        <v>1.0574018126888218</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="B9" s="13">
         <f>A9</f>
         <v>45664</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11">
+        <f>(E8 * Prices!D7) / $G8</f>
+        <v>0.52870090634441091</v>
+      </c>
+      <c r="F9" s="11">
+        <f>(F8 * Prices!E7) / G8</f>
+        <v>0.47129909365558914</v>
+      </c>
+      <c r="G9" s="8">
+        <f xml:space="preserve"> $E9 * Prices!$D8 + $F9 * Prices!$E8</f>
+        <v>1.0574018126888218</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
-      <c r="B10" s="6">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
-        <f>(D9 * Prices!D8) / $F9</f>
-        <v>0.50476190476190474</v>
-      </c>
-      <c r="E10" s="11">
-        <f>(E9 * Prices!E8) / F9</f>
-        <v>0.4952380952380952</v>
-      </c>
-      <c r="F10" s="8">
-        <f xml:space="preserve"> $D10 * Prices!$D9 + $E10 * Prices!$E9</f>
-        <v>0.95523809523809522</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="B10" s="13">
         <f>A10</f>
         <v>45665</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11">
+        <f>(E9 * Prices!D8) / $G9</f>
+        <v>0.50476190476190474</v>
+      </c>
+      <c r="F10" s="11">
+        <f>(F9 * Prices!E8) / G9</f>
+        <v>0.4952380952380952</v>
+      </c>
+      <c r="G10" s="8">
+        <f xml:space="preserve"> $E10 * Prices!$D9 + $F10 * Prices!$E9</f>
+        <v>0.95523809523809522</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
-      <c r="B11" s="6">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11">
-        <f>(D10 * Prices!D9) / $F10</f>
-        <v>0.53339980059820546</v>
-      </c>
-      <c r="E11" s="11">
-        <f>(E10 * Prices!E9) / F10</f>
-        <v>0.46660019940179459</v>
-      </c>
-      <c r="F11" s="8">
-        <f xml:space="preserve"> $D11 * Prices!$D10 + $E11 * Prices!$E10</f>
-        <v>1.0568295114656032</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="B11" s="13">
         <f>A11</f>
         <v>45666</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11">
+        <f>(E10 * Prices!D9) / $G10</f>
+        <v>0.53339980059820546</v>
+      </c>
+      <c r="F11" s="11">
+        <f>(F10 * Prices!E9) / G10</f>
+        <v>0.46660019940179459</v>
+      </c>
+      <c r="G11" s="8">
+        <f xml:space="preserve"> $E11 * Prices!$D10 + $F11 * Prices!$E10</f>
+        <v>1.0568295114656032</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="11">
-        <f>(D11 * Prices!D10) / $F11</f>
-        <v>0.50943396226415094</v>
-      </c>
-      <c r="E12" s="11">
-        <f>(E11 * Prices!E10) / F11</f>
-        <v>0.49056603773584906</v>
-      </c>
-      <c r="F12" s="8">
-        <f xml:space="preserve"> $D12 * Prices!$D11 + $E12 * Prices!$E11</f>
-        <v>0.95566037735849063</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="B12" s="13">
         <f>A12</f>
         <v>45667</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11">
+        <f>(E11 * Prices!D10) / $G11</f>
+        <v>0.50943396226415094</v>
+      </c>
+      <c r="F12" s="11">
+        <f>(F11 * Prices!E10) / G11</f>
+        <v>0.49056603773584906</v>
+      </c>
+      <c r="G12" s="8">
+        <f xml:space="preserve"> $E12 * Prices!$D11 + $F12 * Prices!$E11</f>
+        <v>0.95566037735849063</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="11">
-        <f>(D12 * Prices!D11) / $F12</f>
-        <v>0.53800592300098715</v>
-      </c>
-      <c r="E13" s="11">
-        <f>(E12 * Prices!E11) / F12</f>
-        <v>0.46199407699901279</v>
-      </c>
-      <c r="F13" s="8">
-        <f xml:space="preserve"> $D13 * Prices!$D12 + $E13 * Prices!$E12</f>
-        <v>1.0562685093780848</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="B13" s="13">
         <f>A13</f>
         <v>45668</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11">
+        <f>(E12 * Prices!D11) / $G12</f>
+        <v>0.53800592300098715</v>
+      </c>
+      <c r="F13" s="11">
+        <f>(F12 * Prices!E11) / G12</f>
+        <v>0.46199407699901279</v>
+      </c>
+      <c r="G13" s="8">
+        <f xml:space="preserve"> $E13 * Prices!$D12 + $F13 * Prices!$E12</f>
+        <v>1.0562685093780848</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
-      <c r="B14" s="6">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="11">
-        <f>(D13 * Prices!D12) / $F13</f>
-        <v>0.51401869158878499</v>
-      </c>
-      <c r="E14" s="11">
-        <f>(E13 * Prices!E12) / F13</f>
-        <v>0.48598130841121495</v>
-      </c>
-      <c r="F14" s="8">
-        <f xml:space="preserve"> $D14 * Prices!$D13 + $E14 * Prices!$E13</f>
-        <v>0.9560747663551401</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="B14" s="13">
         <f>A14</f>
         <v>45669</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11">
+        <f>(E13 * Prices!D12) / $G13</f>
+        <v>0.51401869158878499</v>
+      </c>
+      <c r="F14" s="11">
+        <f>(F13 * Prices!E12) / G13</f>
+        <v>0.48598130841121495</v>
+      </c>
+      <c r="G14" s="8">
+        <f xml:space="preserve"> $E14 * Prices!$D13 + $F14 * Prices!$E13</f>
+        <v>0.9560747663551401</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
-      <c r="B15" s="6">
-        <v>1</v>
+      <c r="B15" s="14">
+        <f>A15</f>
+        <v>45670</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
       </c>
-      <c r="D15" s="10">
-        <v>0.5</v>
+      <c r="D15" s="6">
+        <v>1</v>
       </c>
       <c r="E15" s="10">
         <v>0.5</v>
       </c>
-      <c r="F15" s="8">
-        <f xml:space="preserve"> $D15 * Prices!$D14 + $E15 * Prices!$E14</f>
+      <c r="F15" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="8">
+        <f xml:space="preserve"> $E15 * Prices!$D14 + $F15 * Prices!$E14</f>
         <v>1.06006006006006</v>
-      </c>
-      <c r="G15" s="14">
-        <f>A15</f>
-        <v>45670</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
-      <c r="B16" s="6">
-        <v>1</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="11">
-        <f>(D15 * Prices!D14) / $F15</f>
-        <v>0.47592067988668552</v>
-      </c>
-      <c r="E16" s="11">
-        <f>(E15 * Prices!E14) / F15</f>
-        <v>0.52407932011331448</v>
-      </c>
-      <c r="F16" s="8">
-        <f xml:space="preserve"> $D16 * Prices!$D15 + $E16 * Prices!$E15</f>
-        <v>0.95184135977337103</v>
-      </c>
-      <c r="G16" s="13">
+      <c r="B16" s="13">
         <f>A16</f>
         <v>45671</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11">
+        <f>(E15 * Prices!D14) / $G15</f>
+        <v>0.47592067988668552</v>
+      </c>
+      <c r="F16" s="11">
+        <f>(F15 * Prices!E14) / G15</f>
+        <v>0.52407932011331448</v>
+      </c>
+      <c r="G16" s="8">
+        <f xml:space="preserve"> $E16 * Prices!$D15 + $F16 * Prices!$E15</f>
+        <v>0.95184135977337103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
-      <c r="B17" s="6">
-        <v>1</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="11">
-        <f>(D16 * Prices!D15) / $F16</f>
-        <v>0.5044642857142857</v>
-      </c>
-      <c r="E17" s="11">
-        <f>(E16 * Prices!E15) / F16</f>
-        <v>0.49553571428571436</v>
-      </c>
-      <c r="F17" s="8">
-        <f xml:space="preserve"> $D17 * Prices!$D16 + $E17 * Prices!$E16</f>
-        <v>1.0595238095238098</v>
-      </c>
-      <c r="G17" s="13">
+      <c r="B17" s="13">
         <f>A17</f>
         <v>45672</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <f>(E16 * Prices!D15) / $G16</f>
+        <v>0.5044642857142857</v>
+      </c>
+      <c r="F17" s="11">
+        <f>(F16 * Prices!E15) / G16</f>
+        <v>0.49553571428571436</v>
+      </c>
+      <c r="G17" s="8">
+        <f xml:space="preserve"> $E17 * Prices!$D16 + $F17 * Prices!$E16</f>
+        <v>1.0595238095238098</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
-      <c r="B18" s="6">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1</v>
-      </c>
-      <c r="D18" s="11">
-        <f>(D17 * Prices!D16) / $F17</f>
-        <v>0.48033707865168523</v>
-      </c>
-      <c r="E18" s="11">
-        <f>(E17 * Prices!E16) / F17</f>
-        <v>0.5196629213483146</v>
-      </c>
-      <c r="F18" s="8">
-        <f xml:space="preserve"> $D18 * Prices!$D17 + $E18 * Prices!$E17</f>
-        <v>0.95224719101123578</v>
-      </c>
-      <c r="G18" s="13">
+      <c r="B18" s="13">
         <f>A18</f>
         <v>45673</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11">
+        <f>(E17 * Prices!D16) / $G17</f>
+        <v>0.48033707865168523</v>
+      </c>
+      <c r="F18" s="11">
+        <f>(F17 * Prices!E16) / G17</f>
+        <v>0.5196629213483146</v>
+      </c>
+      <c r="G18" s="8">
+        <f xml:space="preserve"> $E18 * Prices!$D17 + $F18 * Prices!$E17</f>
+        <v>0.95224719101123578</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
-      <c r="B19" s="6">
-        <v>1</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="11">
-        <f>(D18 * Prices!D17) / $F18</f>
-        <v>0.50884955752212391</v>
-      </c>
-      <c r="E19" s="11">
-        <f>(E18 * Prices!E17) / F18</f>
-        <v>0.4911504424778762</v>
-      </c>
-      <c r="F19" s="8">
-        <f xml:space="preserve"> $D19 * Prices!$D18 + $E19 * Prices!$E18</f>
-        <v>1.0589970501474928</v>
-      </c>
-      <c r="G19" s="13">
+      <c r="B19" s="13">
         <f>A19</f>
         <v>45674</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <f>(E18 * Prices!D17) / $G18</f>
+        <v>0.50884955752212391</v>
+      </c>
+      <c r="F19" s="11">
+        <f>(F18 * Prices!E17) / G18</f>
+        <v>0.4911504424778762</v>
+      </c>
+      <c r="G19" s="8">
+        <f xml:space="preserve"> $E19 * Prices!$D18 + $F19 * Prices!$E18</f>
+        <v>1.0589970501474928</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
-      <c r="B20" s="6">
-        <v>1</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-      <c r="D20" s="11">
-        <f>(D19 * Prices!D18) / $F19</f>
-        <v>0.48467966573816151</v>
-      </c>
-      <c r="E20" s="11">
-        <f>(E19 * Prices!E18) / F19</f>
-        <v>0.51532033426183854</v>
-      </c>
-      <c r="F20" s="8">
-        <f xml:space="preserve"> $D20 * Prices!$D19 + $E20 * Prices!$E19</f>
-        <v>0.9526462395543176</v>
-      </c>
-      <c r="G20" s="13">
+      <c r="B20" s="13">
         <f>A20</f>
         <v>45675</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
+        <f>(E19 * Prices!D18) / $G19</f>
+        <v>0.48467966573816151</v>
+      </c>
+      <c r="F20" s="11">
+        <f>(F19 * Prices!E18) / G19</f>
+        <v>0.51532033426183854</v>
+      </c>
+      <c r="G20" s="8">
+        <f xml:space="preserve"> $E20 * Prices!$D19 + $F20 * Prices!$E19</f>
+        <v>0.9526462395543176</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
-      <c r="B21" s="6">
-        <v>1</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1</v>
-      </c>
-      <c r="D21" s="11">
-        <f>(D20 * Prices!D19) / $F20</f>
-        <v>0.51315789473684204</v>
-      </c>
-      <c r="E21" s="11">
-        <f>(E20 * Prices!E19) / F20</f>
-        <v>0.48684210526315796</v>
-      </c>
-      <c r="F21" s="8">
-        <f xml:space="preserve"> $D21 * Prices!$D20 + $E21 * Prices!$E20</f>
-        <v>1.0584795321637426</v>
-      </c>
-      <c r="G21" s="13">
+      <c r="B21" s="13">
         <f>A21</f>
         <v>45676</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
+        <f>(E20 * Prices!D19) / $G20</f>
+        <v>0.51315789473684204</v>
+      </c>
+      <c r="F21" s="11">
+        <f>(F20 * Prices!E19) / G20</f>
+        <v>0.48684210526315796</v>
+      </c>
+      <c r="G21" s="8">
+        <f xml:space="preserve"> $E21 * Prices!$D20 + $F21 * Prices!$E20</f>
+        <v>1.0584795321637426</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
-      <c r="B22" s="6">
-        <v>1</v>
+      <c r="B22" s="14">
+        <f>A22</f>
+        <v>45677</v>
       </c>
       <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="10">
-        <v>0.5</v>
+      <c r="D22" s="6">
+        <v>1</v>
       </c>
       <c r="E22" s="10">
         <v>0.5</v>
       </c>
-      <c r="F22" s="8">
-        <f xml:space="preserve"> $D22 * Prices!$D21 + $E22 * Prices!$E21</f>
+      <c r="F22" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="8">
+        <f xml:space="preserve"> $E22 * Prices!$D21 + $F22 * Prices!$E21</f>
         <v>0.95423728813559316</v>
-      </c>
-      <c r="G22" s="14">
-        <f>A22</f>
-        <v>45677</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
-      <c r="B23" s="6">
-        <v>1</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1</v>
-      </c>
-      <c r="D23" s="11">
-        <f>(D22 * Prices!D21) / $F22</f>
-        <v>0.52841918294849022</v>
-      </c>
-      <c r="E23" s="11">
-        <f>(E22 * Prices!E21) / F22</f>
-        <v>0.47158081705150978</v>
-      </c>
-      <c r="F23" s="8">
-        <f xml:space="preserve"> $D23 * Prices!$D22 + $E23 * Prices!$E22</f>
-        <v>1.0568383658969807</v>
-      </c>
-      <c r="G23" s="13">
+      <c r="B23" s="13">
         <f>A23</f>
         <v>45678</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11">
+        <f>(E22 * Prices!D21) / $G22</f>
+        <v>0.52841918294849022</v>
+      </c>
+      <c r="F23" s="11">
+        <f>(F22 * Prices!E21) / G22</f>
+        <v>0.47158081705150978</v>
+      </c>
+      <c r="G23" s="8">
+        <f xml:space="preserve"> $E23 * Prices!$D22 + $F23 * Prices!$E22</f>
+        <v>1.0568383658969807</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
-      <c r="B24" s="6">
-        <v>1</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1</v>
-      </c>
-      <c r="D24" s="11">
-        <f>(D23 * Prices!D22) / $F23</f>
-        <v>0.50420168067226878</v>
-      </c>
-      <c r="E24" s="11">
-        <f>(E23 * Prices!E22) / F23</f>
-        <v>0.49579831932773105</v>
-      </c>
-      <c r="F24" s="8">
-        <f xml:space="preserve"> $D24 * Prices!$D23 + $E24 * Prices!$E23</f>
-        <v>0.95462184873949563</v>
-      </c>
-      <c r="G24" s="13">
+      <c r="B24" s="13">
         <f>A24</f>
         <v>45679</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11">
+        <f>(E23 * Prices!D22) / $G23</f>
+        <v>0.50420168067226878</v>
+      </c>
+      <c r="F24" s="11">
+        <f>(F23 * Prices!E22) / G23</f>
+        <v>0.49579831932773105</v>
+      </c>
+      <c r="G24" s="8">
+        <f xml:space="preserve"> $E24 * Prices!$D23 + $F24 * Prices!$E23</f>
+        <v>0.95462184873949563</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
-      <c r="B25" s="6">
-        <v>1</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1</v>
-      </c>
-      <c r="D25" s="11">
-        <f>(D24 * Prices!D23) / $F24</f>
-        <v>0.53257042253521125</v>
-      </c>
-      <c r="E25" s="11">
-        <f>(E24 * Prices!E23) / F24</f>
-        <v>0.4674295774647888</v>
-      </c>
-      <c r="F25" s="8">
-        <f xml:space="preserve"> $D25 * Prices!$D24 + $E25 * Prices!$E24</f>
-        <v>1.0563380281690142</v>
-      </c>
-      <c r="G25" s="13">
+      <c r="B25" s="13">
         <f>A25</f>
         <v>45680</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11">
+        <f>(E24 * Prices!D23) / $G24</f>
+        <v>0.53257042253521125</v>
+      </c>
+      <c r="F25" s="11">
+        <f>(F24 * Prices!E23) / G24</f>
+        <v>0.4674295774647888</v>
+      </c>
+      <c r="G25" s="8">
+        <f xml:space="preserve"> $E25 * Prices!$D24 + $F25 * Prices!$E24</f>
+        <v>1.0563380281690142</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
-      <c r="B26" s="6">
-        <v>1</v>
-      </c>
-      <c r="C26" s="6">
-        <v>1</v>
-      </c>
-      <c r="D26" s="11">
-        <f>(D25 * Prices!D24) / $F25</f>
-        <v>0.5083333333333333</v>
-      </c>
-      <c r="E26" s="11">
-        <f>(E25 * Prices!E24) / F25</f>
-        <v>0.49166666666666675</v>
-      </c>
-      <c r="F26" s="8">
-        <f xml:space="preserve"> $D26 * Prices!$D25 + $E26 * Prices!$E25</f>
-        <v>0.95500000000000007</v>
-      </c>
-      <c r="G26" s="13">
+      <c r="B26" s="13">
         <f>A26</f>
         <v>45681</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11">
+        <f>(E25 * Prices!D24) / $G25</f>
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="F26" s="11">
+        <f>(F25 * Prices!E24) / G25</f>
+        <v>0.49166666666666675</v>
+      </c>
+      <c r="G26" s="8">
+        <f xml:space="preserve"> $E26 * Prices!$D25 + $F26 * Prices!$E25</f>
+        <v>0.95500000000000007</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
-      <c r="B27" s="6">
-        <v>1</v>
-      </c>
-      <c r="C27" s="6">
-        <v>1</v>
-      </c>
-      <c r="D27" s="11">
-        <f>(D26 * Prices!D25) / $F26</f>
-        <v>0.53664921465968574</v>
-      </c>
-      <c r="E27" s="11">
-        <f>(E26 * Prices!E25) / F26</f>
-        <v>0.46335078534031415</v>
-      </c>
-      <c r="F27" s="8">
-        <f xml:space="preserve"> $D27 * Prices!$D26 + $E27 * Prices!$E26</f>
-        <v>1.0558464223385688</v>
-      </c>
-      <c r="G27" s="13">
+      <c r="B27" s="13">
         <f>A27</f>
         <v>45682</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11">
+        <f>(E26 * Prices!D25) / $G26</f>
+        <v>0.53664921465968574</v>
+      </c>
+      <c r="F27" s="11">
+        <f>(F26 * Prices!E25) / G26</f>
+        <v>0.46335078534031415</v>
+      </c>
+      <c r="G27" s="8">
+        <f xml:space="preserve"> $E27 * Prices!$D26 + $F27 * Prices!$E26</f>
+        <v>1.0558464223385688</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
-      <c r="B28" s="6">
-        <v>1</v>
-      </c>
-      <c r="C28" s="6">
-        <v>1</v>
-      </c>
-      <c r="D28" s="11">
-        <f>(D27 * Prices!D26) / $F27</f>
-        <v>0.51239669421487588</v>
-      </c>
-      <c r="E28" s="11">
-        <f>(E27 * Prices!E26) / F27</f>
-        <v>0.48760330578512406</v>
-      </c>
-      <c r="F28" s="8">
-        <f xml:space="preserve"> $D28 * Prices!$D27 + $E28 * Prices!$E27</f>
-        <v>0.95537190082644619</v>
-      </c>
-      <c r="G28" s="13">
+      <c r="B28" s="13">
         <f>A28</f>
         <v>45683</v>
+      </c>
+      <c r="C28" s="6">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11">
+        <f>(E27 * Prices!D26) / $G27</f>
+        <v>0.51239669421487588</v>
+      </c>
+      <c r="F28" s="11">
+        <f>(F27 * Prices!E26) / G27</f>
+        <v>0.48760330578512406</v>
+      </c>
+      <c r="G28" s="8">
+        <f xml:space="preserve"> $E28 * Prices!$D27 + $F28 * Prices!$E27</f>
+        <v>0.95537190082644619</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
-      <c r="B29" s="6">
-        <v>1</v>
+      <c r="B29" s="14">
+        <f>A29</f>
+        <v>45684</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
       </c>
-      <c r="D29" s="10">
-        <v>0.5</v>
+      <c r="D29" s="6">
+        <v>1</v>
       </c>
       <c r="E29" s="10">
         <v>0.5</v>
       </c>
-      <c r="F29" s="8">
-        <f xml:space="preserve"> $D29 * Prices!$D28 + $E29 * Prices!$E28</f>
+      <c r="F29" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="8">
+        <f xml:space="preserve"> $E29 * Prices!$D28 + $F29 * Prices!$E28</f>
         <v>1.0595555555555556</v>
-      </c>
-      <c r="G29" s="14">
-        <f>A29</f>
-        <v>45684</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
-      <c r="B30" s="6">
-        <v>1</v>
-      </c>
-      <c r="C30" s="6">
-        <v>1</v>
-      </c>
-      <c r="D30" s="11">
-        <f>(D29 * Prices!D28) / $F29</f>
-        <v>0.47567114093959728</v>
-      </c>
-      <c r="E30" s="11">
-        <f>(E29 * Prices!E28) / F29</f>
-        <v>0.52432885906040272</v>
-      </c>
-      <c r="F30" s="8">
-        <f xml:space="preserve"> $D30 * Prices!$D29 + $E30 * Prices!$E29</f>
-        <v>0.95134228187919456</v>
-      </c>
-      <c r="G30" s="13">
+      <c r="B30" s="13">
         <f>A30</f>
         <v>45685</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11">
+        <f>(E29 * Prices!D28) / $G29</f>
+        <v>0.47567114093959728</v>
+      </c>
+      <c r="F30" s="11">
+        <f>(F29 * Prices!E28) / G29</f>
+        <v>0.52432885906040272</v>
+      </c>
+      <c r="G30" s="8">
+        <f xml:space="preserve"> $E30 * Prices!$D29 + $F30 * Prices!$E29</f>
+        <v>0.95134228187919456</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1</v>
-      </c>
-      <c r="D31" s="11">
-        <f>(D30 * Prices!D29) / $F30</f>
-        <v>0.50396825396825395</v>
-      </c>
-      <c r="E31" s="11">
-        <f>(E30 * Prices!E29) / F30</f>
-        <v>0.4960317460317461</v>
-      </c>
-      <c r="F31" s="8">
-        <f xml:space="preserve"> $D31 * Prices!$D30 + $E31 * Prices!$E30</f>
-        <v>1.0590828924162259</v>
-      </c>
-      <c r="G31" s="13">
+      <c r="B31" s="13">
         <f>A31</f>
         <v>45686</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11">
+        <f>(E30 * Prices!D29) / $G30</f>
+        <v>0.50396825396825395</v>
+      </c>
+      <c r="F31" s="11">
+        <f>(F30 * Prices!E29) / G30</f>
+        <v>0.4960317460317461</v>
+      </c>
+      <c r="G31" s="8">
+        <f xml:space="preserve"> $E31 * Prices!$D30 + $F31 * Prices!$E30</f>
+        <v>1.0590828924162259</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
-      <c r="B32" s="6">
-        <v>1</v>
-      </c>
-      <c r="C32" s="6">
-        <v>1</v>
-      </c>
-      <c r="D32" s="11">
-        <f>(D31 * Prices!D30) / $F31</f>
-        <v>0.47960033305578675</v>
-      </c>
-      <c r="E32" s="11">
-        <f>(E31 * Prices!E30) / F31</f>
-        <v>0.52039966694421314</v>
-      </c>
-      <c r="F32" s="8">
-        <f xml:space="preserve"> $D32 * Prices!$D31 + $E32 * Prices!$E31</f>
-        <v>0.95170691090757686</v>
-      </c>
-      <c r="G32" s="13">
+      <c r="B32" s="13">
         <f>A32</f>
         <v>45687</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="11">
+        <f>(E31 * Prices!D30) / $G31</f>
+        <v>0.47960033305578675</v>
+      </c>
+      <c r="F32" s="11">
+        <f>(F31 * Prices!E30) / G31</f>
+        <v>0.52039966694421314</v>
+      </c>
+      <c r="G32" s="8">
+        <f xml:space="preserve"> $E32 * Prices!$D31 + $F32 * Prices!$E31</f>
+        <v>0.95170691090757686</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
-      <c r="B33" s="6">
-        <v>1</v>
-      </c>
-      <c r="C33" s="6">
-        <v>1</v>
-      </c>
-      <c r="D33" s="11">
-        <f>(D32 * Prices!D31) / $F32</f>
-        <v>0.50787401574803148</v>
-      </c>
-      <c r="E33" s="11">
-        <f>(E32 * Prices!E31) / F32</f>
-        <v>0.49212598425196857</v>
-      </c>
-      <c r="F33" s="8">
-        <f xml:space="preserve"> $D33 * Prices!$D32 + $E33 * Prices!$E32</f>
-        <v>1.0586176727909011</v>
-      </c>
-      <c r="G33" s="13">
+      <c r="B33" s="13">
         <f>A33</f>
         <v>45688</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="11">
+        <f>(E32 * Prices!D31) / $G32</f>
+        <v>0.50787401574803148</v>
+      </c>
+      <c r="F33" s="11">
+        <f>(F32 * Prices!E31) / G32</f>
+        <v>0.49212598425196857</v>
+      </c>
+      <c r="G33" s="8">
+        <f xml:space="preserve"> $E33 * Prices!$D32 + $F33 * Prices!$E32</f>
+        <v>1.0586176727909011</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>45689</v>
       </c>
-      <c r="B34" s="6">
-        <v>1</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1</v>
-      </c>
-      <c r="D34" s="11">
-        <f>(D33 * Prices!D32) / $F33</f>
-        <v>0.48347107438016529</v>
-      </c>
-      <c r="E34" s="11">
-        <f>(E33 * Prices!E32) / F33</f>
-        <v>0.51652892561983488</v>
-      </c>
-      <c r="F34" s="8">
-        <f xml:space="preserve"> $D34 * Prices!$D33 + $E34 * Prices!$E33</f>
-        <v>0.95206611570247945</v>
-      </c>
-      <c r="G34" s="13">
+      <c r="B34" s="13">
         <f>A34</f>
         <v>45689</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11">
+        <f>(E33 * Prices!D32) / $G33</f>
+        <v>0.48347107438016529</v>
+      </c>
+      <c r="F34" s="11">
+        <f>(F33 * Prices!E32) / G33</f>
+        <v>0.51652892561983488</v>
+      </c>
+      <c r="G34" s="8">
+        <f xml:space="preserve"> $E34 * Prices!$D33 + $F34 * Prices!$E33</f>
+        <v>0.95206611570247945</v>
       </c>
     </row>
   </sheetData>
@@ -2309,7 +2309,7 @@
         <v>0.9</v>
       </c>
       <c r="D3" s="8">
-        <f>D2 * Expected_Weights!F4</f>
+        <f>D2 * Expected_Weights!G4</f>
         <v>0.95500000000000007</v>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="8">
-        <f>D3 * Expected_Weights!F5</f>
+        <f>D3 * Expected_Weights!G5</f>
         <v>1.01</v>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
         <v>0.9</v>
       </c>
       <c r="D5" s="8">
-        <f>D4 * Expected_Weights!F6</f>
+        <f>D4 * Expected_Weights!G6</f>
         <v>0.96500000000000008</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="8">
-        <f>D5 * Expected_Weights!F7</f>
+        <f>D5 * Expected_Weights!G7</f>
         <v>1.0200000000000002</v>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>0.9</v>
       </c>
       <c r="D7" s="8">
-        <f>D6 * Expected_Weights!F8</f>
+        <f>D6 * Expected_Weights!G8</f>
         <v>0.97390384615384629</v>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="8">
-        <f>D7 * Expected_Weights!F9</f>
+        <f>D7 * Expected_Weights!G9</f>
         <v>1.0298076923076924</v>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>0.9</v>
       </c>
       <c r="D9" s="8">
-        <f>D8 * Expected_Weights!F10</f>
+        <f>D8 * Expected_Weights!G10</f>
         <v>0.98371153846153858</v>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="8">
-        <f>D9 * Expected_Weights!F11</f>
+        <f>D9 * Expected_Weights!G11</f>
         <v>1.0396153846153848</v>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         <v>0.9</v>
       </c>
       <c r="D11" s="8">
-        <f>D10 * Expected_Weights!F12</f>
+        <f>D10 * Expected_Weights!G12</f>
         <v>0.99351923076923099</v>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="8">
-        <f>D11 * Expected_Weights!F13</f>
+        <f>D11 * Expected_Weights!G13</f>
         <v>1.049423076923077</v>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
         <v>0.9</v>
       </c>
       <c r="D13" s="8">
-        <f>D12 * Expected_Weights!F14</f>
+        <f>D12 * Expected_Weights!G14</f>
         <v>1.0033269230769231</v>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="8">
-        <f>D13 * Expected_Weights!F15</f>
+        <f>D13 * Expected_Weights!G15</f>
         <v>1.0635867983367984</v>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
         <v>0.9</v>
       </c>
       <c r="D15" s="8">
-        <f>D14 * Expected_Weights!F16</f>
+        <f>D14 * Expected_Weights!G16</f>
         <v>1.0123659043659043</v>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="8">
-        <f>D15 * Expected_Weights!F17</f>
+        <f>D15 * Expected_Weights!G17</f>
         <v>1.0726257796257799</v>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
         <v>0.9</v>
       </c>
       <c r="D17" s="8">
-        <f>D16 * Expected_Weights!F18</f>
+        <f>D16 * Expected_Weights!G18</f>
         <v>1.0214048856548856</v>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="8">
-        <f>D17 * Expected_Weights!F19</f>
+        <f>D17 * Expected_Weights!G19</f>
         <v>1.0816647609147612</v>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
         <v>0.9</v>
       </c>
       <c r="D19" s="8">
-        <f>D18 * Expected_Weights!F20</f>
+        <f>D18 * Expected_Weights!G20</f>
         <v>1.0304438669438671</v>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="8">
-        <f>D19 * Expected_Weights!F21</f>
+        <f>D19 * Expected_Weights!G21</f>
         <v>1.0907037422037422</v>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
         <v>0.9</v>
       </c>
       <c r="D21" s="8">
-        <f>D20 * Expected_Weights!F22</f>
+        <f>D20 * Expected_Weights!G22</f>
         <v>1.0407901811198421</v>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="8">
-        <f>D21 * Expected_Weights!F23</f>
+        <f>D21 * Expected_Weights!G23</f>
         <v>1.0999469942563165</v>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>0.9</v>
       </c>
       <c r="D23" s="8">
-        <f>D22 * Expected_Weights!F24</f>
+        <f>D22 * Expected_Weights!G24</f>
         <v>1.0500334331724162</v>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="8">
-        <f>D23 * Expected_Weights!F25</f>
+        <f>D23 * Expected_Weights!G25</f>
         <v>1.1091902463088905</v>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         <v>0.9</v>
       </c>
       <c r="D25" s="8">
-        <f>D24 * Expected_Weights!F26</f>
+        <f>D24 * Expected_Weights!G26</f>
         <v>1.0592766852249904</v>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="8">
-        <f>D25 * Expected_Weights!F27</f>
+        <f>D25 * Expected_Weights!G27</f>
         <v>1.1184334983614646</v>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
         <v>0.9</v>
       </c>
       <c r="D27" s="8">
-        <f>D26 * Expected_Weights!F28</f>
+        <f>D26 * Expected_Weights!G28</f>
         <v>1.0685199372775644</v>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="8">
-        <f>D27 * Expected_Weights!F29</f>
+        <f>D27 * Expected_Weights!G29</f>
         <v>1.1321562357643171</v>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
         <v>0.9</v>
       </c>
       <c r="D29" s="8">
-        <f>D28 * Expected_Weights!F30</f>
+        <f>D28 * Expected_Weights!G30</f>
         <v>1.0770680967757849</v>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="8">
-        <f>D29 * Expected_Weights!F31</f>
+        <f>D29 * Expected_Weights!G31</f>
         <v>1.1407043952625378</v>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
         <v>0.9</v>
       </c>
       <c r="D31" s="8">
-        <f>D30 * Expected_Weights!F32</f>
+        <f>D30 * Expected_Weights!G32</f>
         <v>1.0856162562740053</v>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="8">
-        <f>D31 * Expected_Weights!F33</f>
+        <f>D31 * Expected_Weights!G33</f>
         <v>1.1492525547607579</v>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
         <v>0.9</v>
       </c>
       <c r="D33" s="8">
-        <f>D32 * Expected_Weights!F34</f>
+        <f>D32 * Expected_Weights!G34</f>
         <v>1.0941644157722259</v>
       </c>
     </row>
@@ -2935,16 +2935,16 @@
         <v>82.08</v>
       </c>
       <c r="I4" s="5">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="J4">
-        <v>2.2599999999999998</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="K4" s="5">
-        <v>-4.5</v>
+        <v>-4.87</v>
       </c>
       <c r="L4" s="5">
-        <v>-4.1900000000000004</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="M4" t="s">
         <v>34</v>

--- a/public/tests/data/test_rb.xlsx
+++ b/public/tests/data/test_rb.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4484F7D5-D0AE-4C5D-94F8-A32F13F9AB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13C79BB-2496-4E91-B91A-111B07D5FFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Portfolios" sheetId="2" r:id="rId2"/>
-    <sheet name="Assets" sheetId="4" r:id="rId3"/>
-    <sheet name="Prices" sheetId="5" r:id="rId4"/>
+    <sheet name="Assets" sheetId="4" r:id="rId2"/>
+    <sheet name="Prices" sheetId="5" r:id="rId3"/>
+    <sheet name="Portfolios" sheetId="2" r:id="rId4"/>
     <sheet name="Expected_Weights" sheetId="7" r:id="rId5"/>
     <sheet name="Expected_Values" sheetId="6" r:id="rId6"/>
     <sheet name="Expected_Stats" sheetId="10" r:id="rId7"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Name</t>
   </si>
@@ -89,12 +89,6 @@
     <t>P1</t>
   </si>
   <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -140,12 +134,6 @@
     <t>full</t>
   </si>
   <si>
-    <t>inf</t>
-  </si>
-  <si>
-    <t>0 days</t>
-  </si>
-  <si>
     <t>1 days</t>
   </si>
   <si>
@@ -173,13 +161,10 @@
     <t>_grow</t>
   </si>
   <si>
-    <t>_P3</t>
-  </si>
-  <si>
-    <t>monthly</t>
-  </si>
-  <si>
     <t>_WD</t>
+  </si>
+  <si>
+    <t>_P1</t>
   </si>
 </sst>
 </file>
@@ -191,7 +176,7 @@
     <numFmt numFmtId="169" formatCode="0.0000%"/>
     <numFmt numFmtId="173" formatCode="[$]dddd" x16r2:formatCode16="[$-en-SE]dddd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,13 +186,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -232,9 +210,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -243,7 +220,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -256,10 +232,10 @@
     <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -578,7 +554,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -586,7 +562,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -598,84 +574,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="10.3046875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C271D88-DDEC-4A65-8905-A99CA73725FC}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -712,13 +610,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1942483-BB80-4E18-92F0-22F7848078C4}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.23046875" style="8"/>
+    <col min="4" max="4" width="9.23046875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -731,11 +629,11 @@
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>41</v>
+      <c r="D1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
@@ -748,10 +646,10 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>0</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>0</v>
       </c>
     </row>
@@ -765,11 +663,11 @@
       <c r="C3">
         <v>90</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <f>B3/B2</f>
         <v>1.01</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <f>C3/C2</f>
         <v>0.9</v>
       </c>
@@ -784,11 +682,11 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <f t="shared" ref="D4:D10" si="0">B4/B3</f>
         <v>1.0099009900990099</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <f t="shared" ref="E4:E10" si="1">C4/C3</f>
         <v>1.1111111111111112</v>
       </c>
@@ -803,11 +701,11 @@
       <c r="C5">
         <v>90</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <f t="shared" si="0"/>
         <v>1.0098039215686274</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -822,11 +720,11 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f t="shared" si="0"/>
         <v>1.0097087378640777</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
@@ -841,11 +739,11 @@
       <c r="C7">
         <v>90</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <f t="shared" si="0"/>
         <v>1.0096153846153846</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -860,11 +758,11 @@
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <f t="shared" si="0"/>
         <v>1.0095238095238095</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
@@ -879,11 +777,11 @@
       <c r="C9">
         <v>90</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <f t="shared" si="0"/>
         <v>1.0094339622641511</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
@@ -898,11 +796,11 @@
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <f t="shared" si="0"/>
         <v>1.0093457943925233</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <f t="shared" si="1"/>
         <v>1.1111111111111112</v>
       </c>
@@ -917,11 +815,11 @@
       <c r="C11">
         <v>90</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f t="shared" ref="D11:D20" si="2">B11/B10</f>
         <v>1.0092592592592593</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f t="shared" ref="E11:E20" si="3">C11/C10</f>
         <v>0.9</v>
       </c>
@@ -936,11 +834,11 @@
       <c r="C12">
         <v>100</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <f t="shared" si="2"/>
         <v>1.0091743119266054</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <f t="shared" si="3"/>
         <v>1.1111111111111112</v>
       </c>
@@ -955,11 +853,11 @@
       <c r="C13">
         <v>90</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <f t="shared" si="2"/>
         <v>1.009090909090909</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
@@ -974,11 +872,11 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <f t="shared" si="2"/>
         <v>1.0090090090090089</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <f t="shared" si="3"/>
         <v>1.1111111111111112</v>
       </c>
@@ -993,11 +891,11 @@
       <c r="C15">
         <v>90</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <f t="shared" si="2"/>
         <v>1.0089285714285714</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
@@ -1012,11 +910,11 @@
       <c r="C16">
         <v>100</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <f t="shared" si="2"/>
         <v>1.0088495575221239</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <f t="shared" si="3"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1031,11 +929,11 @@
       <c r="C17">
         <v>90</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <f t="shared" si="2"/>
         <v>1.0087719298245614</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
@@ -1050,11 +948,11 @@
       <c r="C18">
         <v>100</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <f t="shared" si="2"/>
         <v>1.008695652173913</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <f t="shared" si="3"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1069,11 +967,11 @@
       <c r="C19">
         <v>90</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <f t="shared" si="2"/>
         <v>1.0086206896551724</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
@@ -1088,11 +986,11 @@
       <c r="C20">
         <v>100</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <f t="shared" si="2"/>
         <v>1.0085470085470085</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <f t="shared" si="3"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1107,11 +1005,11 @@
       <c r="C21">
         <v>90</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <f t="shared" ref="D21:D33" si="4">B21/B20</f>
         <v>1.0084745762711864</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="7">
         <f t="shared" ref="E21:E33" si="5">C21/C20</f>
         <v>0.9</v>
       </c>
@@ -1126,11 +1024,11 @@
       <c r="C22">
         <v>100</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <f t="shared" si="4"/>
         <v>1.0084033613445378</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="7">
         <f t="shared" si="5"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1145,11 +1043,11 @@
       <c r="C23">
         <v>90</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <f t="shared" si="4"/>
         <v>1.0083333333333333</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="7">
         <f t="shared" si="5"/>
         <v>0.9</v>
       </c>
@@ -1164,11 +1062,11 @@
       <c r="C24">
         <v>100</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <f t="shared" si="4"/>
         <v>1.0082644628099173</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="7">
         <f t="shared" si="5"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1183,11 +1081,11 @@
       <c r="C25">
         <v>90</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <f t="shared" si="4"/>
         <v>1.0081967213114753</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="7">
         <f t="shared" si="5"/>
         <v>0.9</v>
       </c>
@@ -1202,11 +1100,11 @@
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <f t="shared" si="4"/>
         <v>1.0081300813008129</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <f t="shared" si="5"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1221,11 +1119,11 @@
       <c r="C27">
         <v>90</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <f t="shared" si="4"/>
         <v>1.0080645161290323</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <f t="shared" si="5"/>
         <v>0.9</v>
       </c>
@@ -1240,11 +1138,11 @@
       <c r="C28">
         <v>100</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <f t="shared" si="4"/>
         <v>1.008</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <f t="shared" si="5"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1259,11 +1157,11 @@
       <c r="C29">
         <v>90</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <f t="shared" si="4"/>
         <v>1.0079365079365079</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <f t="shared" si="5"/>
         <v>0.9</v>
       </c>
@@ -1278,11 +1176,11 @@
       <c r="C30">
         <v>100</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <f t="shared" si="4"/>
         <v>1.0078740157480315</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="7">
         <f t="shared" si="5"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1297,11 +1195,11 @@
       <c r="C31">
         <v>90</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <f t="shared" si="4"/>
         <v>1.0078125</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="7">
         <f t="shared" si="5"/>
         <v>0.9</v>
       </c>
@@ -1316,11 +1214,11 @@
       <c r="C32">
         <v>100</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <f t="shared" si="4"/>
         <v>1.0077519379844961</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="7">
         <f t="shared" si="5"/>
         <v>1.1111111111111112</v>
       </c>
@@ -1335,13 +1233,66 @@
       <c r="C33">
         <v>90</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <f t="shared" si="4"/>
         <v>1.0076923076923077</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <f t="shared" si="5"/>
         <v>0.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.3046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1351,908 +1302,704 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.4609375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E2" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <f>A3</f>
         <v>45658</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
-        <v>1</v>
-      </c>
-      <c r="E3" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="F3" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <f>A4</f>
         <v>45659</v>
       </c>
-      <c r="C4" s="6">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="11">
+      <c r="C4" s="10">
         <v>0.5</v>
       </c>
-      <c r="F4" s="11">
+      <c r="D4" s="10">
         <v>0.5</v>
       </c>
-      <c r="G4" s="8">
-        <f xml:space="preserve"> $E4 * Prices!$D3 + $F4 * Prices!$E3</f>
+      <c r="E4" s="7">
+        <f xml:space="preserve"> $C4 * Prices!$D3 + $D4 * Prices!$E3</f>
         <v>0.95500000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <f>A5</f>
         <v>45660</v>
       </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="11">
-        <f>(E4 * Prices!D3) / $G4</f>
+      <c r="C5" s="10">
+        <f>(C4 * Prices!D3) / $E4</f>
         <v>0.52879581151832455</v>
       </c>
-      <c r="F5" s="11">
-        <f>(F4 * Prices!E3) / $G4</f>
+      <c r="D5" s="10">
+        <f>(D4 * Prices!E3) / $E4</f>
         <v>0.47120418848167539</v>
       </c>
-      <c r="G5" s="8">
-        <f xml:space="preserve"> $E5 * Prices!$D4 + $F5 * Prices!$E4</f>
+      <c r="E5" s="7">
+        <f xml:space="preserve"> $C5 * Prices!$D4 + $D5 * Prices!$E4</f>
         <v>1.0575916230366491</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <f>A6</f>
         <v>45661</v>
       </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="11">
-        <f>(E5 * Prices!D4) / $G5</f>
+      <c r="C6" s="10">
+        <f>(C5 * Prices!D4) / $E5</f>
         <v>0.50495049504950495</v>
       </c>
-      <c r="F6" s="11">
-        <f>(F5 * Prices!E4) / G5</f>
+      <c r="D6" s="10">
+        <f>(D5 * Prices!E4) / E5</f>
         <v>0.4950495049504951</v>
       </c>
-      <c r="G6" s="8">
-        <f xml:space="preserve"> $E6 * Prices!$D5 + $F6 * Prices!$E5</f>
+      <c r="E6" s="7">
+        <f xml:space="preserve"> $C6 * Prices!$D5 + $D6 * Prices!$E5</f>
         <v>0.95544554455445552</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
         <f>A7</f>
         <v>45662</v>
       </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="11">
-        <f>(E6 * Prices!D5) / $G6</f>
+      <c r="C7" s="10">
+        <f>(C6 * Prices!D5) / $E6</f>
         <v>0.53367875647668395</v>
       </c>
-      <c r="F7" s="11">
-        <f>(F6 * Prices!E5) / G6</f>
+      <c r="D7" s="10">
+        <f>(D6 * Prices!E5) / E6</f>
         <v>0.46632124352331611</v>
       </c>
-      <c r="G7" s="8">
-        <f xml:space="preserve"> $E7 * Prices!$D6 + $F7 * Prices!$E6</f>
+      <c r="E7" s="7">
+        <f xml:space="preserve"> $C7 * Prices!$D6 + $D7 * Prices!$E6</f>
         <v>1.0569948186528499</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <f>A8</f>
         <v>45663</v>
       </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="C8" s="9">
         <v>0.5</v>
       </c>
-      <c r="F8" s="10">
+      <c r="D8" s="9">
         <v>0.5</v>
       </c>
-      <c r="G8" s="8">
-        <f xml:space="preserve"> $E8 * Prices!$D7 + $F8 * Prices!$E7</f>
+      <c r="E8" s="7">
+        <f xml:space="preserve"> $C8 * Prices!$D7 + $D8 * Prices!$E7</f>
         <v>0.95480769230769225</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <f>A9</f>
         <v>45664</v>
       </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11">
-        <f>(E8 * Prices!D7) / $G8</f>
+      <c r="C9" s="10">
+        <f>(C8 * Prices!D7) / $E8</f>
         <v>0.52870090634441091</v>
       </c>
-      <c r="F9" s="11">
-        <f>(F8 * Prices!E7) / G8</f>
+      <c r="D9" s="10">
+        <f>(D8 * Prices!E7) / E8</f>
         <v>0.47129909365558914</v>
       </c>
-      <c r="G9" s="8">
-        <f xml:space="preserve"> $E9 * Prices!$D8 + $F9 * Prices!$E8</f>
+      <c r="E9" s="7">
+        <f xml:space="preserve"> $C9 * Prices!$D8 + $D9 * Prices!$E8</f>
         <v>1.0574018126888218</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <f>A10</f>
         <v>45665</v>
       </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="11">
-        <f>(E9 * Prices!D8) / $G9</f>
+      <c r="C10" s="10">
+        <f>(C9 * Prices!D8) / $E9</f>
         <v>0.50476190476190474</v>
       </c>
-      <c r="F10" s="11">
-        <f>(F9 * Prices!E8) / G9</f>
+      <c r="D10" s="10">
+        <f>(D9 * Prices!E8) / E9</f>
         <v>0.4952380952380952</v>
       </c>
-      <c r="G10" s="8">
-        <f xml:space="preserve"> $E10 * Prices!$D9 + $F10 * Prices!$E9</f>
+      <c r="E10" s="7">
+        <f xml:space="preserve"> $C10 * Prices!$D9 + $D10 * Prices!$E9</f>
         <v>0.95523809523809522</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <f>A11</f>
         <v>45666</v>
       </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11">
-        <f>(E10 * Prices!D9) / $G10</f>
+      <c r="C11" s="10">
+        <f>(C10 * Prices!D9) / $E10</f>
         <v>0.53339980059820546</v>
       </c>
-      <c r="F11" s="11">
-        <f>(F10 * Prices!E9) / G10</f>
+      <c r="D11" s="10">
+        <f>(D10 * Prices!E9) / E10</f>
         <v>0.46660019940179459</v>
       </c>
-      <c r="G11" s="8">
-        <f xml:space="preserve"> $E11 * Prices!$D10 + $F11 * Prices!$E10</f>
+      <c r="E11" s="7">
+        <f xml:space="preserve"> $C11 * Prices!$D10 + $D11 * Prices!$E10</f>
         <v>1.0568295114656032</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <f>A12</f>
         <v>45667</v>
       </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="11">
-        <f>(E11 * Prices!D10) / $G11</f>
+      <c r="C12" s="10">
+        <f>(C11 * Prices!D10) / $E11</f>
         <v>0.50943396226415094</v>
       </c>
-      <c r="F12" s="11">
-        <f>(F11 * Prices!E10) / G11</f>
+      <c r="D12" s="10">
+        <f>(D11 * Prices!E10) / E11</f>
         <v>0.49056603773584906</v>
       </c>
-      <c r="G12" s="8">
-        <f xml:space="preserve"> $E12 * Prices!$D11 + $F12 * Prices!$E11</f>
+      <c r="E12" s="7">
+        <f xml:space="preserve"> $C12 * Prices!$D11 + $D12 * Prices!$E11</f>
         <v>0.95566037735849063</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <f>A13</f>
         <v>45668</v>
       </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11">
-        <f>(E12 * Prices!D11) / $G12</f>
+      <c r="C13" s="10">
+        <f>(C12 * Prices!D11) / $E12</f>
         <v>0.53800592300098715</v>
       </c>
-      <c r="F13" s="11">
-        <f>(F12 * Prices!E11) / G12</f>
+      <c r="D13" s="10">
+        <f>(D12 * Prices!E11) / E12</f>
         <v>0.46199407699901279</v>
       </c>
-      <c r="G13" s="8">
-        <f xml:space="preserve"> $E13 * Prices!$D12 + $F13 * Prices!$E12</f>
+      <c r="E13" s="7">
+        <f xml:space="preserve"> $C13 * Prices!$D12 + $D13 * Prices!$E12</f>
         <v>1.0562685093780848</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <f>A14</f>
         <v>45669</v>
       </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="11">
-        <f>(E13 * Prices!D12) / $G13</f>
+      <c r="C14" s="10">
+        <f>(C13 * Prices!D12) / $E13</f>
         <v>0.51401869158878499</v>
       </c>
-      <c r="F14" s="11">
-        <f>(F13 * Prices!E12) / G13</f>
+      <c r="D14" s="10">
+        <f>(D13 * Prices!E12) / E13</f>
         <v>0.48598130841121495</v>
       </c>
-      <c r="G14" s="8">
-        <f xml:space="preserve"> $E14 * Prices!$D13 + $F14 * Prices!$E13</f>
+      <c r="E14" s="7">
+        <f xml:space="preserve"> $C14 * Prices!$D13 + $D14 * Prices!$E13</f>
         <v>0.9560747663551401</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <f>A15</f>
         <v>45670</v>
       </c>
-      <c r="C15" s="6">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10">
+      <c r="C15" s="9">
         <v>0.5</v>
       </c>
-      <c r="F15" s="10">
+      <c r="D15" s="9">
         <v>0.5</v>
       </c>
-      <c r="G15" s="8">
-        <f xml:space="preserve"> $E15 * Prices!$D14 + $F15 * Prices!$E14</f>
+      <c r="E15" s="7">
+        <f xml:space="preserve"> $C15 * Prices!$D14 + $D15 * Prices!$E14</f>
         <v>1.06006006006006</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <f>A16</f>
         <v>45671</v>
       </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="11">
-        <f>(E15 * Prices!D14) / $G15</f>
+      <c r="C16" s="10">
+        <f>(C15 * Prices!D14) / $E15</f>
         <v>0.47592067988668552</v>
       </c>
-      <c r="F16" s="11">
-        <f>(F15 * Prices!E14) / G15</f>
+      <c r="D16" s="10">
+        <f>(D15 * Prices!E14) / E15</f>
         <v>0.52407932011331448</v>
       </c>
-      <c r="G16" s="8">
-        <f xml:space="preserve"> $E16 * Prices!$D15 + $F16 * Prices!$E15</f>
+      <c r="E16" s="7">
+        <f xml:space="preserve"> $C16 * Prices!$D15 + $D16 * Prices!$E15</f>
         <v>0.95184135977337103</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <f>A17</f>
         <v>45672</v>
       </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="11">
-        <f>(E16 * Prices!D15) / $G16</f>
+      <c r="C17" s="10">
+        <f>(C16 * Prices!D15) / $E16</f>
         <v>0.5044642857142857</v>
       </c>
-      <c r="F17" s="11">
-        <f>(F16 * Prices!E15) / G16</f>
+      <c r="D17" s="10">
+        <f>(D16 * Prices!E15) / E16</f>
         <v>0.49553571428571436</v>
       </c>
-      <c r="G17" s="8">
-        <f xml:space="preserve"> $E17 * Prices!$D16 + $F17 * Prices!$E16</f>
+      <c r="E17" s="7">
+        <f xml:space="preserve"> $C17 * Prices!$D16 + $D17 * Prices!$E16</f>
         <v>1.0595238095238098</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <f>A18</f>
         <v>45673</v>
       </c>
-      <c r="C18" s="6">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="11">
-        <f>(E17 * Prices!D16) / $G17</f>
+      <c r="C18" s="10">
+        <f>(C17 * Prices!D16) / $E17</f>
         <v>0.48033707865168523</v>
       </c>
-      <c r="F18" s="11">
-        <f>(F17 * Prices!E16) / G17</f>
+      <c r="D18" s="10">
+        <f>(D17 * Prices!E16) / E17</f>
         <v>0.5196629213483146</v>
       </c>
-      <c r="G18" s="8">
-        <f xml:space="preserve"> $E18 * Prices!$D17 + $F18 * Prices!$E17</f>
+      <c r="E18" s="7">
+        <f xml:space="preserve"> $C18 * Prices!$D17 + $D18 * Prices!$E17</f>
         <v>0.95224719101123578</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="12">
         <f>A19</f>
         <v>45674</v>
       </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11">
-        <f>(E18 * Prices!D17) / $G18</f>
+      <c r="C19" s="10">
+        <f>(C18 * Prices!D17) / $E18</f>
         <v>0.50884955752212391</v>
       </c>
-      <c r="F19" s="11">
-        <f>(F18 * Prices!E17) / G18</f>
+      <c r="D19" s="10">
+        <f>(D18 * Prices!E17) / E18</f>
         <v>0.4911504424778762</v>
       </c>
-      <c r="G19" s="8">
-        <f xml:space="preserve"> $E19 * Prices!$D18 + $F19 * Prices!$E18</f>
+      <c r="E19" s="7">
+        <f xml:space="preserve"> $C19 * Prices!$D18 + $D19 * Prices!$E18</f>
         <v>1.0589970501474928</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <f>A20</f>
         <v>45675</v>
       </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11">
-        <f>(E19 * Prices!D18) / $G19</f>
+      <c r="C20" s="10">
+        <f>(C19 * Prices!D18) / $E19</f>
         <v>0.48467966573816151</v>
       </c>
-      <c r="F20" s="11">
-        <f>(F19 * Prices!E18) / G19</f>
+      <c r="D20" s="10">
+        <f>(D19 * Prices!E18) / E19</f>
         <v>0.51532033426183854</v>
       </c>
-      <c r="G20" s="8">
-        <f xml:space="preserve"> $E20 * Prices!$D19 + $F20 * Prices!$E19</f>
+      <c r="E20" s="7">
+        <f xml:space="preserve"> $C20 * Prices!$D19 + $D20 * Prices!$E19</f>
         <v>0.9526462395543176</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="12">
         <f>A21</f>
         <v>45676</v>
       </c>
-      <c r="C21" s="6">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11">
-        <f>(E20 * Prices!D19) / $G20</f>
+      <c r="C21" s="10">
+        <f>(C20 * Prices!D19) / $E20</f>
         <v>0.51315789473684204</v>
       </c>
-      <c r="F21" s="11">
-        <f>(F20 * Prices!E19) / G20</f>
+      <c r="D21" s="10">
+        <f>(D20 * Prices!E19) / E20</f>
         <v>0.48684210526315796</v>
       </c>
-      <c r="G21" s="8">
-        <f xml:space="preserve"> $E21 * Prices!$D20 + $F21 * Prices!$E20</f>
+      <c r="E21" s="7">
+        <f xml:space="preserve"> $C21 * Prices!$D20 + $D21 * Prices!$E20</f>
         <v>1.0584795321637426</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <f>A22</f>
         <v>45677</v>
       </c>
-      <c r="C22" s="6">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10">
+      <c r="C22" s="9">
         <v>0.5</v>
       </c>
-      <c r="F22" s="10">
+      <c r="D22" s="9">
         <v>0.5</v>
       </c>
-      <c r="G22" s="8">
-        <f xml:space="preserve"> $E22 * Prices!$D21 + $F22 * Prices!$E21</f>
+      <c r="E22" s="7">
+        <f xml:space="preserve"> $C22 * Prices!$D21 + $D22 * Prices!$E21</f>
         <v>0.95423728813559316</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="12">
         <f>A23</f>
         <v>45678</v>
       </c>
-      <c r="C23" s="6">
-        <v>1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="11">
-        <f>(E22 * Prices!D21) / $G22</f>
+      <c r="C23" s="10">
+        <f>(C22 * Prices!D21) / $E22</f>
         <v>0.52841918294849022</v>
       </c>
-      <c r="F23" s="11">
-        <f>(F22 * Prices!E21) / G22</f>
+      <c r="D23" s="10">
+        <f>(D22 * Prices!E21) / E22</f>
         <v>0.47158081705150978</v>
       </c>
-      <c r="G23" s="8">
-        <f xml:space="preserve"> $E23 * Prices!$D22 + $F23 * Prices!$E22</f>
+      <c r="E23" s="7">
+        <f xml:space="preserve"> $C23 * Prices!$D22 + $D23 * Prices!$E22</f>
         <v>1.0568383658969807</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="12">
         <f>A24</f>
         <v>45679</v>
       </c>
-      <c r="C24" s="6">
-        <v>1</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-      <c r="E24" s="11">
-        <f>(E23 * Prices!D22) / $G23</f>
+      <c r="C24" s="10">
+        <f>(C23 * Prices!D22) / $E23</f>
         <v>0.50420168067226878</v>
       </c>
-      <c r="F24" s="11">
-        <f>(F23 * Prices!E22) / G23</f>
+      <c r="D24" s="10">
+        <f>(D23 * Prices!E22) / E23</f>
         <v>0.49579831932773105</v>
       </c>
-      <c r="G24" s="8">
-        <f xml:space="preserve"> $E24 * Prices!$D23 + $F24 * Prices!$E23</f>
+      <c r="E24" s="7">
+        <f xml:space="preserve"> $C24 * Prices!$D23 + $D24 * Prices!$E23</f>
         <v>0.95462184873949563</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="12">
         <f>A25</f>
         <v>45680</v>
       </c>
-      <c r="C25" s="6">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11">
-        <f>(E24 * Prices!D23) / $G24</f>
+      <c r="C25" s="10">
+        <f>(C24 * Prices!D23) / $E24</f>
         <v>0.53257042253521125</v>
       </c>
-      <c r="F25" s="11">
-        <f>(F24 * Prices!E23) / G24</f>
+      <c r="D25" s="10">
+        <f>(D24 * Prices!E23) / E24</f>
         <v>0.4674295774647888</v>
       </c>
-      <c r="G25" s="8">
-        <f xml:space="preserve"> $E25 * Prices!$D24 + $F25 * Prices!$E24</f>
+      <c r="E25" s="7">
+        <f xml:space="preserve"> $C25 * Prices!$D24 + $D25 * Prices!$E24</f>
         <v>1.0563380281690142</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="12">
         <f>A26</f>
         <v>45681</v>
       </c>
-      <c r="C26" s="6">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="11">
-        <f>(E25 * Prices!D24) / $G25</f>
+      <c r="C26" s="10">
+        <f>(C25 * Prices!D24) / $E25</f>
         <v>0.5083333333333333</v>
       </c>
-      <c r="F26" s="11">
-        <f>(F25 * Prices!E24) / G25</f>
+      <c r="D26" s="10">
+        <f>(D25 * Prices!E24) / E25</f>
         <v>0.49166666666666675</v>
       </c>
-      <c r="G26" s="8">
-        <f xml:space="preserve"> $E26 * Prices!$D25 + $F26 * Prices!$E25</f>
+      <c r="E26" s="7">
+        <f xml:space="preserve"> $C26 * Prices!$D25 + $D26 * Prices!$E25</f>
         <v>0.95500000000000007</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="12">
         <f>A27</f>
         <v>45682</v>
       </c>
-      <c r="C27" s="6">
-        <v>1</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11">
-        <f>(E26 * Prices!D25) / $G26</f>
+      <c r="C27" s="10">
+        <f>(C26 * Prices!D25) / $E26</f>
         <v>0.53664921465968574</v>
       </c>
-      <c r="F27" s="11">
-        <f>(F26 * Prices!E25) / G26</f>
+      <c r="D27" s="10">
+        <f>(D26 * Prices!E25) / E26</f>
         <v>0.46335078534031415</v>
       </c>
-      <c r="G27" s="8">
-        <f xml:space="preserve"> $E27 * Prices!$D26 + $F27 * Prices!$E26</f>
+      <c r="E27" s="7">
+        <f xml:space="preserve"> $C27 * Prices!$D26 + $D27 * Prices!$E26</f>
         <v>1.0558464223385688</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="12">
         <f>A28</f>
         <v>45683</v>
       </c>
-      <c r="C28" s="6">
-        <v>1</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-      <c r="E28" s="11">
-        <f>(E27 * Prices!D26) / $G27</f>
+      <c r="C28" s="10">
+        <f>(C27 * Prices!D26) / $E27</f>
         <v>0.51239669421487588</v>
       </c>
-      <c r="F28" s="11">
-        <f>(F27 * Prices!E26) / G27</f>
+      <c r="D28" s="10">
+        <f>(D27 * Prices!E26) / E27</f>
         <v>0.48760330578512406</v>
       </c>
-      <c r="G28" s="8">
-        <f xml:space="preserve"> $E28 * Prices!$D27 + $F28 * Prices!$E27</f>
+      <c r="E28" s="7">
+        <f xml:space="preserve"> $C28 * Prices!$D27 + $D28 * Prices!$E27</f>
         <v>0.95537190082644619</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="13">
         <f>A29</f>
         <v>45684</v>
       </c>
-      <c r="C29" s="6">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="C29" s="9">
         <v>0.5</v>
       </c>
-      <c r="F29" s="10">
+      <c r="D29" s="9">
         <v>0.5</v>
       </c>
-      <c r="G29" s="8">
-        <f xml:space="preserve"> $E29 * Prices!$D28 + $F29 * Prices!$E28</f>
+      <c r="E29" s="7">
+        <f xml:space="preserve"> $C29 * Prices!$D28 + $D29 * Prices!$E28</f>
         <v>1.0595555555555556</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="12">
         <f>A30</f>
         <v>45685</v>
       </c>
-      <c r="C30" s="6">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
-      <c r="E30" s="11">
-        <f>(E29 * Prices!D28) / $G29</f>
+      <c r="C30" s="10">
+        <f>(C29 * Prices!D28) / $E29</f>
         <v>0.47567114093959728</v>
       </c>
-      <c r="F30" s="11">
-        <f>(F29 * Prices!E28) / G29</f>
+      <c r="D30" s="10">
+        <f>(D29 * Prices!E28) / E29</f>
         <v>0.52432885906040272</v>
       </c>
-      <c r="G30" s="8">
-        <f xml:space="preserve"> $E30 * Prices!$D29 + $F30 * Prices!$E29</f>
+      <c r="E30" s="7">
+        <f xml:space="preserve"> $C30 * Prices!$D29 + $D30 * Prices!$E29</f>
         <v>0.95134228187919456</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="12">
         <f>A31</f>
         <v>45686</v>
       </c>
-      <c r="C31" s="6">
-        <v>1</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-      <c r="E31" s="11">
-        <f>(E30 * Prices!D29) / $G30</f>
+      <c r="C31" s="10">
+        <f>(C30 * Prices!D29) / $E30</f>
         <v>0.50396825396825395</v>
       </c>
-      <c r="F31" s="11">
-        <f>(F30 * Prices!E29) / G30</f>
+      <c r="D31" s="10">
+        <f>(D30 * Prices!E29) / E30</f>
         <v>0.4960317460317461</v>
       </c>
-      <c r="G31" s="8">
-        <f xml:space="preserve"> $E31 * Prices!$D30 + $F31 * Prices!$E30</f>
+      <c r="E31" s="7">
+        <f xml:space="preserve"> $C31 * Prices!$D30 + $D31 * Prices!$E30</f>
         <v>1.0590828924162259</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="12">
         <f>A32</f>
         <v>45687</v>
       </c>
-      <c r="C32" s="6">
-        <v>1</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
-      <c r="E32" s="11">
-        <f>(E31 * Prices!D30) / $G31</f>
+      <c r="C32" s="10">
+        <f>(C31 * Prices!D30) / $E31</f>
         <v>0.47960033305578675</v>
       </c>
-      <c r="F32" s="11">
-        <f>(F31 * Prices!E30) / G31</f>
+      <c r="D32" s="10">
+        <f>(D31 * Prices!E30) / E31</f>
         <v>0.52039966694421314</v>
       </c>
-      <c r="G32" s="8">
-        <f xml:space="preserve"> $E32 * Prices!$D31 + $F32 * Prices!$E31</f>
+      <c r="E32" s="7">
+        <f xml:space="preserve"> $C32 * Prices!$D31 + $D32 * Prices!$E31</f>
         <v>0.95170691090757686</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="12">
         <f>A33</f>
         <v>45688</v>
       </c>
-      <c r="C33" s="6">
-        <v>1</v>
-      </c>
-      <c r="D33" s="6">
-        <v>1</v>
-      </c>
-      <c r="E33" s="11">
-        <f>(E32 * Prices!D31) / $G32</f>
+      <c r="C33" s="10">
+        <f>(C32 * Prices!D31) / $E32</f>
         <v>0.50787401574803148</v>
       </c>
-      <c r="F33" s="11">
-        <f>(F32 * Prices!E31) / G32</f>
+      <c r="D33" s="10">
+        <f>(D32 * Prices!E31) / E32</f>
         <v>0.49212598425196857</v>
       </c>
-      <c r="G33" s="8">
-        <f xml:space="preserve"> $E33 * Prices!$D32 + $F33 * Prices!$E32</f>
+      <c r="E33" s="7">
+        <f xml:space="preserve"> $C33 * Prices!$D32 + $D33 * Prices!$E32</f>
         <v>1.0586176727909011</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>45689</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="12">
         <f>A34</f>
         <v>45689</v>
       </c>
-      <c r="C34" s="6">
-        <v>1</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1</v>
-      </c>
-      <c r="E34" s="11">
-        <f>(E33 * Prices!D32) / $G33</f>
+      <c r="C34" s="10">
+        <f>(C33 * Prices!D32) / $E33</f>
         <v>0.48347107438016529</v>
       </c>
-      <c r="F34" s="11">
-        <f>(F33 * Prices!E32) / G33</f>
+      <c r="D34" s="10">
+        <f>(D33 * Prices!E32) / E33</f>
         <v>0.51652892561983488</v>
       </c>
-      <c r="G34" s="8">
-        <f xml:space="preserve"> $E34 * Prices!$D33 + $F34 * Prices!$E33</f>
+      <c r="E34" s="7">
+        <f xml:space="preserve"> $C34 * Prices!$D33 + $D34 * Prices!$E33</f>
         <v>0.95206611570247945</v>
       </c>
     </row>
@@ -2263,503 +2010,305 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9E8070-11EC-4D5B-882F-63D06BDC939E}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="9.23046875" style="8"/>
+    <col min="2" max="2" width="9.23046875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45658</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="8">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45659</v>
       </c>
-      <c r="B3" s="8">
-        <v>1.01</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D3" s="8">
-        <f>D2 * Expected_Weights!G4</f>
+      <c r="B3" s="7">
+        <f>B2 * Expected_Weights!E4</f>
         <v>0.95500000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
-      <c r="B4" s="8">
-        <v>1.02</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1</v>
-      </c>
-      <c r="D4" s="8">
-        <f>D3 * Expected_Weights!G5</f>
+      <c r="B4" s="7">
+        <f>B3 * Expected_Weights!E5</f>
         <v>1.01</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45661</v>
       </c>
-      <c r="B5" s="8">
-        <v>1.03</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D5" s="8">
-        <f>D4 * Expected_Weights!G6</f>
+      <c r="B5" s="7">
+        <f>B4 * Expected_Weights!E6</f>
         <v>0.96500000000000008</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45662</v>
       </c>
-      <c r="B6" s="8">
-        <v>1.04</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8">
-        <f>D5 * Expected_Weights!G7</f>
+      <c r="B6" s="7">
+        <f>B5 * Expected_Weights!E7</f>
         <v>1.0200000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45663</v>
       </c>
-      <c r="B7" s="8">
-        <v>1.05</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D7" s="8">
-        <f>D6 * Expected_Weights!G8</f>
+      <c r="B7" s="7">
+        <f>B6 * Expected_Weights!E8</f>
         <v>0.97390384615384629</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45664</v>
       </c>
-      <c r="B8" s="8">
-        <v>1.06</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <f>D7 * Expected_Weights!G9</f>
+      <c r="B8" s="7">
+        <f>B7 * Expected_Weights!E9</f>
         <v>1.0298076923076924</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45665</v>
       </c>
-      <c r="B9" s="8">
-        <v>1.07</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D9" s="8">
-        <f>D8 * Expected_Weights!G10</f>
+      <c r="B9" s="7">
+        <f>B8 * Expected_Weights!E10</f>
         <v>0.98371153846153858</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45666</v>
       </c>
-      <c r="B10" s="8">
-        <v>1.08</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <f>D9 * Expected_Weights!G11</f>
+      <c r="B10" s="7">
+        <f>B9 * Expected_Weights!E11</f>
         <v>1.0396153846153848</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
-      <c r="B11" s="8">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D11" s="8">
-        <f>D10 * Expected_Weights!G12</f>
+      <c r="B11" s="7">
+        <f>B10 * Expected_Weights!E12</f>
         <v>0.99351923076923099</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45668</v>
       </c>
-      <c r="B12" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <f>D11 * Expected_Weights!G13</f>
+      <c r="B12" s="7">
+        <f>B11 * Expected_Weights!E13</f>
         <v>1.049423076923077</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45669</v>
       </c>
-      <c r="B13" s="8">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D13" s="8">
-        <f>D12 * Expected_Weights!G14</f>
+      <c r="B13" s="7">
+        <f>B12 * Expected_Weights!E14</f>
         <v>1.0033269230769231</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45670</v>
       </c>
-      <c r="B14" s="8">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8">
-        <f>D13 * Expected_Weights!G15</f>
+      <c r="B14" s="7">
+        <f>B13 * Expected_Weights!E15</f>
         <v>1.0635867983367984</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45671</v>
       </c>
-      <c r="B15" s="8">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D15" s="8">
-        <f>D14 * Expected_Weights!G16</f>
+      <c r="B15" s="7">
+        <f>B14 * Expected_Weights!E16</f>
         <v>1.0123659043659043</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45672</v>
       </c>
-      <c r="B16" s="8">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1</v>
-      </c>
-      <c r="D16" s="8">
-        <f>D15 * Expected_Weights!G17</f>
+      <c r="B16" s="7">
+        <f>B15 * Expected_Weights!E17</f>
         <v>1.0726257796257799</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45673</v>
       </c>
-      <c r="B17" s="8">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D17" s="8">
-        <f>D16 * Expected_Weights!G18</f>
+      <c r="B17" s="7">
+        <f>B16 * Expected_Weights!E18</f>
         <v>1.0214048856548856</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
-      <c r="B18" s="8">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <f>D17 * Expected_Weights!G19</f>
+      <c r="B18" s="7">
+        <f>B17 * Expected_Weights!E19</f>
         <v>1.0816647609147612</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45675</v>
       </c>
-      <c r="B19" s="8">
-        <v>1.17</v>
-      </c>
-      <c r="C19" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D19" s="8">
-        <f>D18 * Expected_Weights!G20</f>
+      <c r="B19" s="7">
+        <f>B18 * Expected_Weights!E20</f>
         <v>1.0304438669438671</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45676</v>
       </c>
-      <c r="B20" s="8">
-        <v>1.18</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8">
-        <f>D19 * Expected_Weights!G21</f>
+      <c r="B20" s="7">
+        <f>B19 * Expected_Weights!E21</f>
         <v>1.0907037422037422</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45677</v>
       </c>
-      <c r="B21" s="8">
-        <v>1.19</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D21" s="8">
-        <f>D20 * Expected_Weights!G22</f>
+      <c r="B21" s="7">
+        <f>B20 * Expected_Weights!E22</f>
         <v>1.0407901811198421</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45678</v>
       </c>
-      <c r="B22" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="C22" s="8">
-        <v>1</v>
-      </c>
-      <c r="D22" s="8">
-        <f>D21 * Expected_Weights!G23</f>
+      <c r="B22" s="7">
+        <f>B21 * Expected_Weights!E23</f>
         <v>1.0999469942563165</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45679</v>
       </c>
-      <c r="B23" s="8">
-        <v>1.21</v>
-      </c>
-      <c r="C23" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D23" s="8">
-        <f>D22 * Expected_Weights!G24</f>
+      <c r="B23" s="7">
+        <f>B22 * Expected_Weights!E24</f>
         <v>1.0500334331724162</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45680</v>
       </c>
-      <c r="B24" s="8">
-        <v>1.22</v>
-      </c>
-      <c r="C24" s="8">
-        <v>1</v>
-      </c>
-      <c r="D24" s="8">
-        <f>D23 * Expected_Weights!G25</f>
+      <c r="B24" s="7">
+        <f>B23 * Expected_Weights!E25</f>
         <v>1.1091902463088905</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
-      <c r="B25" s="8">
-        <v>1.23</v>
-      </c>
-      <c r="C25" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D25" s="8">
-        <f>D24 * Expected_Weights!G26</f>
+      <c r="B25" s="7">
+        <f>B24 * Expected_Weights!E26</f>
         <v>1.0592766852249904</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45682</v>
       </c>
-      <c r="B26" s="8">
-        <v>1.24</v>
-      </c>
-      <c r="C26" s="8">
-        <v>1</v>
-      </c>
-      <c r="D26" s="8">
-        <f>D25 * Expected_Weights!G27</f>
+      <c r="B26" s="7">
+        <f>B25 * Expected_Weights!E27</f>
         <v>1.1184334983614646</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45683</v>
       </c>
-      <c r="B27" s="8">
-        <v>1.25</v>
-      </c>
-      <c r="C27" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D27" s="8">
-        <f>D26 * Expected_Weights!G28</f>
+      <c r="B27" s="7">
+        <f>B26 * Expected_Weights!E28</f>
         <v>1.0685199372775644</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45684</v>
       </c>
-      <c r="B28" s="8">
-        <v>1.26</v>
-      </c>
-      <c r="C28" s="8">
-        <v>1</v>
-      </c>
-      <c r="D28" s="8">
-        <f>D27 * Expected_Weights!G29</f>
+      <c r="B28" s="7">
+        <f>B27 * Expected_Weights!E29</f>
         <v>1.1321562357643171</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45685</v>
       </c>
-      <c r="B29" s="8">
-        <v>1.27</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D29" s="8">
-        <f>D28 * Expected_Weights!G30</f>
+      <c r="B29" s="7">
+        <f>B28 * Expected_Weights!E30</f>
         <v>1.0770680967757849</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45686</v>
       </c>
-      <c r="B30" s="8">
-        <v>1.28</v>
-      </c>
-      <c r="C30" s="8">
-        <v>1</v>
-      </c>
-      <c r="D30" s="8">
-        <f>D29 * Expected_Weights!G31</f>
+      <c r="B30" s="7">
+        <f>B29 * Expected_Weights!E31</f>
         <v>1.1407043952625378</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45687</v>
       </c>
-      <c r="B31" s="8">
-        <v>1.29</v>
-      </c>
-      <c r="C31" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D31" s="8">
-        <f>D30 * Expected_Weights!G32</f>
+      <c r="B31" s="7">
+        <f>B30 * Expected_Weights!E32</f>
         <v>1.0856162562740053</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
-      <c r="B32" s="8">
-        <v>1.3</v>
-      </c>
-      <c r="C32" s="8">
-        <v>1</v>
-      </c>
-      <c r="D32" s="8">
-        <f>D31 * Expected_Weights!G33</f>
+      <c r="B32" s="7">
+        <f>B31 * Expected_Weights!E33</f>
         <v>1.1492525547607579</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45689</v>
       </c>
-      <c r="B33" s="8">
-        <v>1.31</v>
-      </c>
-      <c r="C33" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D33" s="8">
-        <f>D32 * Expected_Weights!G34</f>
+      <c r="B33" s="7">
+        <f>B32 * Expected_Weights!E34</f>
         <v>1.0941644157722259</v>
       </c>
     </row>
@@ -2770,7 +2319,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9C66B4-691D-4E6C-9B58-26BA46864B57}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.07421875" bestFit="1" customWidth="1"/>
@@ -2790,40 +2339,40 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="N1" s="1"/>
     </row>
@@ -2837,117 +2386,35 @@
       <c r="C2" s="2">
         <v>45689</v>
       </c>
-      <c r="D2" t="s">
-        <v>39</v>
+      <c r="D2" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2" s="5">
-        <v>31</v>
+        <v>9.42</v>
       </c>
       <c r="G2" s="5">
-        <v>2308.36</v>
+        <v>188.72</v>
       </c>
       <c r="H2" s="5">
-        <v>2.67</v>
+        <v>82.08</v>
       </c>
       <c r="I2" s="5">
-        <v>79.53</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
+        <v>1.26</v>
+      </c>
+      <c r="J2">
+        <v>2.0099999999999998</v>
       </c>
       <c r="K2" s="5">
-        <v>0</v>
+        <v>-4.87</v>
       </c>
       <c r="L2" s="5">
-        <v>0</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45658</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45689</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="5">
-        <v>-10</v>
-      </c>
-      <c r="G3" s="5">
-        <v>-71.099999999999994</v>
-      </c>
-      <c r="H3" s="5">
-        <v>167.17</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0.31</v>
-      </c>
-      <c r="J3">
-        <v>0.47</v>
-      </c>
-      <c r="K3" s="5">
-        <v>-10</v>
-      </c>
-      <c r="L3" s="5">
-        <v>-10</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2">
-        <v>45658</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45689</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="5">
-        <v>9.42</v>
-      </c>
-      <c r="G4" s="5">
-        <v>188.72</v>
-      </c>
-      <c r="H4" s="5">
-        <v>82.08</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1.26</v>
-      </c>
-      <c r="J4">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="K4" s="5">
-        <v>-4.87</v>
-      </c>
-      <c r="L4" s="5">
-        <v>-4.5999999999999996</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/public/tests/data/test_rb.xlsx
+++ b/public/tests/data/test_rb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13C79BB-2496-4E91-B91A-111B07D5FFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A612213-4A60-40CC-8F96-04A413AE04A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -89,6 +89,9 @@
     <t>P1</t>
   </si>
   <si>
+    <t>P2</t>
+  </si>
+  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -161,10 +164,16 @@
     <t>_grow</t>
   </si>
   <si>
+    <t>monthly</t>
+  </si>
+  <si>
     <t>_WD</t>
   </si>
   <si>
     <t>_P1</t>
+  </si>
+  <si>
+    <t>_P2</t>
   </si>
 </sst>
 </file>
@@ -554,7 +563,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -562,7 +571,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -630,10 +639,10 @@
         <v>9</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
@@ -1249,49 +1258,64 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955DA01E-A3C8-43F7-BE2B-2D20BB66CB4A}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="B3" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C4" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="3">
         <v>0.5</v>
       </c>
     </row>
@@ -1302,20 +1326,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93EA1201-9593-4FA8-BE4A-D6543E3F5A5B}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.4609375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>14</v>
@@ -1324,15 +1349,24 @@
         <v>14</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+        <v>42</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>8</v>
@@ -1341,10 +1375,19 @@
         <v>9</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+        <v>39</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45658</v>
       </c>
@@ -1361,8 +1404,17 @@
       <c r="E3" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F3" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45659</v>
       </c>
@@ -1380,8 +1432,18 @@
         <f xml:space="preserve"> $C4 * Prices!$D3 + $D4 * Prices!$E3</f>
         <v>0.95500000000000007</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F4" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="7">
+        <f xml:space="preserve"> $F4 * Prices!$D3 + $G4 * Prices!$E3</f>
+        <v>0.95500000000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
@@ -1401,8 +1463,20 @@
         <f xml:space="preserve"> $C5 * Prices!$D4 + $D5 * Prices!$E4</f>
         <v>1.0575916230366491</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F5" s="10">
+        <f>(F4 * Prices!D3) / $H4</f>
+        <v>0.52879581151832455</v>
+      </c>
+      <c r="G5" s="10">
+        <f>(G4 * Prices!E3) / $H4</f>
+        <v>0.47120418848167539</v>
+      </c>
+      <c r="H5" s="7">
+        <f xml:space="preserve"> $F5 * Prices!$D4 + $G5 * Prices!$E4</f>
+        <v>1.0575916230366491</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45661</v>
       </c>
@@ -1422,8 +1496,20 @@
         <f xml:space="preserve"> $C6 * Prices!$D5 + $D6 * Prices!$E5</f>
         <v>0.95544554455445552</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F6" s="10">
+        <f>(F5 * Prices!D4) / $H5</f>
+        <v>0.50495049504950495</v>
+      </c>
+      <c r="G6" s="10">
+        <f>(G5 * Prices!E4) / $H5</f>
+        <v>0.4950495049504951</v>
+      </c>
+      <c r="H6" s="7">
+        <f xml:space="preserve"> $F6 * Prices!$D5 + $G6 * Prices!$E5</f>
+        <v>0.95544554455445552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45662</v>
       </c>
@@ -1443,8 +1529,20 @@
         <f xml:space="preserve"> $C7 * Prices!$D6 + $D7 * Prices!$E6</f>
         <v>1.0569948186528499</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F7" s="10">
+        <f>(F6 * Prices!D5) / $H6</f>
+        <v>0.53367875647668395</v>
+      </c>
+      <c r="G7" s="10">
+        <f>(G6 * Prices!E5) / $H6</f>
+        <v>0.46632124352331611</v>
+      </c>
+      <c r="H7" s="7">
+        <f xml:space="preserve"> $F7 * Prices!$D6 + $G7 * Prices!$E6</f>
+        <v>1.0569948186528499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45663</v>
       </c>
@@ -1462,8 +1560,20 @@
         <f xml:space="preserve"> $C8 * Prices!$D7 + $D8 * Prices!$E7</f>
         <v>0.95480769230769225</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F8" s="10">
+        <f>(F7 * Prices!D6) / $H7</f>
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="G8" s="10">
+        <f>(G7 * Prices!E6) / $H7</f>
+        <v>0.49019607843137253</v>
+      </c>
+      <c r="H8" s="7">
+        <f xml:space="preserve"> $F8 * Prices!$D7 + $G8 * Prices!$E7</f>
+        <v>0.95588235294117641</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45664</v>
       </c>
@@ -1483,8 +1593,20 @@
         <f xml:space="preserve"> $C9 * Prices!$D8 + $D9 * Prices!$E8</f>
         <v>1.0574018126888218</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F9" s="10">
+        <f>(F8 * Prices!D7) / $H8</f>
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="G9" s="10">
+        <f>(G8 * Prices!E7) / $H8</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="H9" s="7">
+        <f xml:space="preserve"> $F9 * Prices!$D8 + $G9 * Prices!$E8</f>
+        <v>1.0564102564102564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45665</v>
       </c>
@@ -1504,8 +1626,20 @@
         <f xml:space="preserve"> $C10 * Prices!$D9 + $D10 * Prices!$E9</f>
         <v>0.95523809523809522</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F10" s="10">
+        <f>(F9 * Prices!D8) / $H9</f>
+        <v>0.5145631067961165</v>
+      </c>
+      <c r="G10" s="10">
+        <f>(G9 * Prices!E8) / $H9</f>
+        <v>0.48543689320388356</v>
+      </c>
+      <c r="H10" s="7">
+        <f xml:space="preserve"> $F10 * Prices!$D9 + $G10 * Prices!$E9</f>
+        <v>0.95631067961165073</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45666</v>
       </c>
@@ -1525,8 +1659,20 @@
         <f xml:space="preserve"> $C11 * Prices!$D10 + $D11 * Prices!$E10</f>
         <v>1.0568295114656032</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F11" s="10">
+        <f>(F10 * Prices!D9) / $H10</f>
+        <v>0.54314720812182737</v>
+      </c>
+      <c r="G11" s="10">
+        <f>(G10 * Prices!E9) / $H10</f>
+        <v>0.45685279187817257</v>
+      </c>
+      <c r="H11" s="7">
+        <f xml:space="preserve"> $F11 * Prices!$D10 + $G11 * Prices!$E10</f>
+        <v>1.0558375634517765</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
@@ -1546,8 +1692,20 @@
         <f xml:space="preserve"> $C12 * Prices!$D11 + $D12 * Prices!$E11</f>
         <v>0.95566037735849063</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F12" s="10">
+        <f>(F11 * Prices!D10) / $H11</f>
+        <v>0.51923076923076916</v>
+      </c>
+      <c r="G12" s="10">
+        <f>(G11 * Prices!E10) / $H11</f>
+        <v>0.48076923076923084</v>
+      </c>
+      <c r="H12" s="7">
+        <f xml:space="preserve"> $F12 * Prices!$D11 + $G12 * Prices!$E11</f>
+        <v>0.95673076923076916</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45668</v>
       </c>
@@ -1567,8 +1725,20 @@
         <f xml:space="preserve"> $C13 * Prices!$D12 + $D13 * Prices!$E12</f>
         <v>1.0562685093780848</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F13" s="10">
+        <f>(F12 * Prices!D11) / $H12</f>
+        <v>0.54773869346733661</v>
+      </c>
+      <c r="G13" s="10">
+        <f>(G12 * Prices!E11) / $H12</f>
+        <v>0.45226130653266344</v>
+      </c>
+      <c r="H13" s="7">
+        <f xml:space="preserve"> $F13 * Prices!$D12 + $G13 * Prices!$E12</f>
+        <v>1.0552763819095479</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45669</v>
       </c>
@@ -1588,8 +1758,20 @@
         <f xml:space="preserve"> $C14 * Prices!$D13 + $D14 * Prices!$E13</f>
         <v>0.9560747663551401</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F14" s="10">
+        <f>(F13 * Prices!D12) / $H13</f>
+        <v>0.52380952380952372</v>
+      </c>
+      <c r="G14" s="10">
+        <f>(G13 * Prices!E12) / $H13</f>
+        <v>0.47619047619047628</v>
+      </c>
+      <c r="H14" s="7">
+        <f xml:space="preserve"> $F14 * Prices!$D13 + $G14 * Prices!$E13</f>
+        <v>0.95714285714285707</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45670</v>
       </c>
@@ -1607,8 +1789,20 @@
         <f xml:space="preserve"> $C15 * Prices!$D14 + $D15 * Prices!$E14</f>
         <v>1.06006006006006</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F15" s="10">
+        <f>(F14 * Prices!D13) / $H14</f>
+        <v>0.55223880597014918</v>
+      </c>
+      <c r="G15" s="10">
+        <f>(G14 * Prices!E13) / $H14</f>
+        <v>0.44776119402985087</v>
+      </c>
+      <c r="H15" s="7">
+        <f xml:space="preserve"> $F15 * Prices!$D14 + $G15 * Prices!$E14</f>
+        <v>1.0547263681592041</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45671</v>
       </c>
@@ -1628,8 +1822,20 @@
         <f xml:space="preserve"> $C16 * Prices!$D15 + $D16 * Prices!$E15</f>
         <v>0.95184135977337103</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F16" s="10">
+        <f>(F15 * Prices!D14) / $H15</f>
+        <v>0.52830188679245271</v>
+      </c>
+      <c r="G16" s="10">
+        <f>(G15 * Prices!E14) / $H15</f>
+        <v>0.47169811320754729</v>
+      </c>
+      <c r="H16" s="7">
+        <f xml:space="preserve"> $F16 * Prices!$D15 + $G16 * Prices!$E15</f>
+        <v>0.95754716981132071</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45672</v>
       </c>
@@ -1649,8 +1855,20 @@
         <f xml:space="preserve"> $C17 * Prices!$D16 + $D17 * Prices!$E16</f>
         <v>1.0595238095238098</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17" s="10">
+        <f>(F16 * Prices!D15) / $H16</f>
+        <v>0.55665024630541859</v>
+      </c>
+      <c r="G17" s="10">
+        <f>(G16 * Prices!E15) / $H16</f>
+        <v>0.44334975369458146</v>
+      </c>
+      <c r="H17" s="7">
+        <f xml:space="preserve"> $F17 * Prices!$D16 + $G17 * Prices!$E16</f>
+        <v>1.0541871921182266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45673</v>
       </c>
@@ -1670,8 +1888,20 @@
         <f xml:space="preserve"> $C18 * Prices!$D17 + $D18 * Prices!$E17</f>
         <v>0.95224719101123578</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F18" s="10">
+        <f>(F17 * Prices!D16) / $H17</f>
+        <v>0.53271028037383161</v>
+      </c>
+      <c r="G18" s="10">
+        <f>(G17 * Prices!E16) / $H17</f>
+        <v>0.46728971962616844</v>
+      </c>
+      <c r="H18" s="7">
+        <f xml:space="preserve"> $F18 * Prices!$D17 + $G18 * Prices!$E17</f>
+        <v>0.95794392523364502</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
@@ -1691,8 +1921,20 @@
         <f xml:space="preserve"> $C19 * Prices!$D18 + $D19 * Prices!$E18</f>
         <v>1.0589970501474928</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F19" s="10">
+        <f>(F18 * Prices!D17) / $H18</f>
+        <v>0.56097560975609739</v>
+      </c>
+      <c r="G19" s="10">
+        <f>(G18 * Prices!E17) / $H18</f>
+        <v>0.43902439024390261</v>
+      </c>
+      <c r="H19" s="7">
+        <f xml:space="preserve"> $F19 * Prices!$D18 + $G19 * Prices!$E18</f>
+        <v>1.0536585365853659</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45675</v>
       </c>
@@ -1712,8 +1954,20 @@
         <f xml:space="preserve"> $C20 * Prices!$D19 + $D20 * Prices!$E19</f>
         <v>0.9526462395543176</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F20" s="10">
+        <f>(F19 * Prices!D18) / $H19</f>
+        <v>0.53703703703703687</v>
+      </c>
+      <c r="G20" s="10">
+        <f>(G19 * Prices!E18) / $H19</f>
+        <v>0.46296296296296313</v>
+      </c>
+      <c r="H20" s="7">
+        <f xml:space="preserve"> $F20 * Prices!$D19 + $G20 * Prices!$E19</f>
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45676</v>
       </c>
@@ -1733,8 +1987,20 @@
         <f xml:space="preserve"> $C21 * Prices!$D20 + $D21 * Prices!$E20</f>
         <v>1.0584795321637426</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F21" s="10">
+        <f>(F20 * Prices!D19) / $H20</f>
+        <v>0.56521739130434767</v>
+      </c>
+      <c r="G21" s="10">
+        <f>(G20 * Prices!E19) / $H20</f>
+        <v>0.43478260869565233</v>
+      </c>
+      <c r="H21" s="7">
+        <f xml:space="preserve"> $F21 * Prices!$D20 + $G21 * Prices!$E20</f>
+        <v>1.0531400966183575</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45677</v>
       </c>
@@ -1752,8 +2018,20 @@
         <f xml:space="preserve"> $C22 * Prices!$D21 + $D22 * Prices!$E21</f>
         <v>0.95423728813559316</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F22" s="10">
+        <f>(F21 * Prices!D20) / $H21</f>
+        <v>0.54128440366972463</v>
+      </c>
+      <c r="G22" s="10">
+        <f>(G21 * Prices!E20) / $H21</f>
+        <v>0.45871559633027542</v>
+      </c>
+      <c r="H22" s="7">
+        <f xml:space="preserve"> $F22 * Prices!$D21 + $G22 * Prices!$E21</f>
+        <v>0.95871559633027525</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45678</v>
       </c>
@@ -1773,8 +2051,20 @@
         <f xml:space="preserve"> $C23 * Prices!$D22 + $D23 * Prices!$E22</f>
         <v>1.0568383658969807</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F23" s="10">
+        <f>(F22 * Prices!D21) / $H22</f>
+        <v>0.56937799043062187</v>
+      </c>
+      <c r="G23" s="10">
+        <f>(G22 * Prices!E21) / $H22</f>
+        <v>0.43062200956937818</v>
+      </c>
+      <c r="H23" s="7">
+        <f xml:space="preserve"> $F23 * Prices!$D22 + $G23 * Prices!$E22</f>
+        <v>1.0526315789473686</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45679</v>
       </c>
@@ -1794,8 +2084,20 @@
         <f xml:space="preserve"> $C24 * Prices!$D23 + $D24 * Prices!$E23</f>
         <v>0.95462184873949563</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F24" s="10">
+        <f>(F23 * Prices!D22) / $H23</f>
+        <v>0.5454545454545453</v>
+      </c>
+      <c r="G24" s="10">
+        <f>(G23 * Prices!E22) / $H23</f>
+        <v>0.4545454545454547</v>
+      </c>
+      <c r="H24" s="7">
+        <f xml:space="preserve"> $F24 * Prices!$D23 + $G24 * Prices!$E23</f>
+        <v>0.95909090909090899</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45680</v>
       </c>
@@ -1815,8 +2117,20 @@
         <f xml:space="preserve"> $C25 * Prices!$D24 + $D25 * Prices!$E24</f>
         <v>1.0563380281690142</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F25" s="10">
+        <f>(F24 * Prices!D23) / $H24</f>
+        <v>0.57345971563981035</v>
+      </c>
+      <c r="G25" s="10">
+        <f>(G24 * Prices!E23) / $H24</f>
+        <v>0.42654028436018976</v>
+      </c>
+      <c r="H25" s="7">
+        <f xml:space="preserve"> $F25 * Prices!$D24 + $G25 * Prices!$E24</f>
+        <v>1.0521327014218009</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
@@ -1836,8 +2150,20 @@
         <f xml:space="preserve"> $C26 * Prices!$D25 + $D26 * Prices!$E25</f>
         <v>0.95500000000000007</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F26" s="10">
+        <f>(F25 * Prices!D24) / $H25</f>
+        <v>0.54954954954954938</v>
+      </c>
+      <c r="G26" s="10">
+        <f>(G25 * Prices!E24) / $H25</f>
+        <v>0.45045045045045068</v>
+      </c>
+      <c r="H26" s="7">
+        <f xml:space="preserve"> $F26 * Prices!$D25 + $G26 * Prices!$E25</f>
+        <v>0.95945945945945943</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45682</v>
       </c>
@@ -1857,8 +2183,20 @@
         <f xml:space="preserve"> $C27 * Prices!$D26 + $D27 * Prices!$E26</f>
         <v>1.0558464223385688</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F27" s="10">
+        <f>(F26 * Prices!D25) / $H26</f>
+        <v>0.57746478873239415</v>
+      </c>
+      <c r="G27" s="10">
+        <f>(G26 * Prices!E25) / $H26</f>
+        <v>0.42253521126760585</v>
+      </c>
+      <c r="H27" s="7">
+        <f xml:space="preserve"> $F27 * Prices!$D26 + $G27 * Prices!$E26</f>
+        <v>1.051643192488263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45683</v>
       </c>
@@ -1878,8 +2216,20 @@
         <f xml:space="preserve"> $C28 * Prices!$D27 + $D28 * Prices!$E27</f>
         <v>0.95537190082644619</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F28" s="10">
+        <f>(F27 * Prices!D26) / $H27</f>
+        <v>0.55357142857142827</v>
+      </c>
+      <c r="G28" s="10">
+        <f>(G27 * Prices!E26) / $H27</f>
+        <v>0.44642857142857167</v>
+      </c>
+      <c r="H28" s="7">
+        <f xml:space="preserve"> $F28 * Prices!$D27 + $G28 * Prices!$E27</f>
+        <v>0.95982142857142849</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45684</v>
       </c>
@@ -1897,8 +2247,20 @@
         <f xml:space="preserve"> $C29 * Prices!$D28 + $D29 * Prices!$E28</f>
         <v>1.0595555555555556</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F29" s="10">
+        <f>(F28 * Prices!D27) / $H28</f>
+        <v>0.581395348837209</v>
+      </c>
+      <c r="G29" s="10">
+        <f>(G28 * Prices!E27) / $H28</f>
+        <v>0.418604651162791</v>
+      </c>
+      <c r="H29" s="7">
+        <f xml:space="preserve"> $F29 * Prices!$D28 + $G29 * Prices!$E28</f>
+        <v>1.0511627906976744</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45685</v>
       </c>
@@ -1918,8 +2280,20 @@
         <f xml:space="preserve"> $C30 * Prices!$D29 + $D30 * Prices!$E29</f>
         <v>0.95134228187919456</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F30" s="10">
+        <f>(F29 * Prices!D28) / $H29</f>
+        <v>0.55752212389380507</v>
+      </c>
+      <c r="G30" s="10">
+        <f>(G29 * Prices!E28) / $H29</f>
+        <v>0.44247787610619504</v>
+      </c>
+      <c r="H30" s="7">
+        <f xml:space="preserve"> $F30 * Prices!$D29 + $G30 * Prices!$E29</f>
+        <v>0.96017699115044253</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45686</v>
       </c>
@@ -1939,8 +2313,20 @@
         <f xml:space="preserve"> $C31 * Prices!$D30 + $D31 * Prices!$E30</f>
         <v>1.0590828924162259</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F31" s="10">
+        <f>(F30 * Prices!D29) / $H30</f>
+        <v>0.58525345622119784</v>
+      </c>
+      <c r="G31" s="10">
+        <f>(G30 * Prices!E29) / $H30</f>
+        <v>0.41474654377880216</v>
+      </c>
+      <c r="H31" s="7">
+        <f xml:space="preserve"> $F31 * Prices!$D30 + $G31 * Prices!$E30</f>
+        <v>1.0506912442396314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45687</v>
       </c>
@@ -1960,8 +2346,20 @@
         <f xml:space="preserve"> $C32 * Prices!$D31 + $D32 * Prices!$E31</f>
         <v>0.95170691090757686</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F32" s="10">
+        <f>(F31 * Prices!D30) / $H31</f>
+        <v>0.56140350877192946</v>
+      </c>
+      <c r="G32" s="10">
+        <f>(G31 * Prices!E30) / $H31</f>
+        <v>0.43859649122807048</v>
+      </c>
+      <c r="H32" s="7">
+        <f xml:space="preserve"> $F32 * Prices!$D31 + $G32 * Prices!$E31</f>
+        <v>0.96052631578947367</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
@@ -1981,8 +2379,20 @@
         <f xml:space="preserve"> $C33 * Prices!$D32 + $D33 * Prices!$E32</f>
         <v>1.0586176727909011</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F33" s="10">
+        <f>(F32 * Prices!D31) / $H32</f>
+        <v>0.58904109589041065</v>
+      </c>
+      <c r="G33" s="10">
+        <f>(G32 * Prices!E31) / $H32</f>
+        <v>0.41095890410958935</v>
+      </c>
+      <c r="H33" s="7">
+        <f xml:space="preserve"> $F33 * Prices!$D32 + $G33 * Prices!$E32</f>
+        <v>1.0502283105022832</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>45689</v>
       </c>
@@ -2001,6 +2411,16 @@
       <c r="E34" s="7">
         <f xml:space="preserve"> $C34 * Prices!$D33 + $D34 * Prices!$E33</f>
         <v>0.95206611570247945</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="7">
+        <f xml:space="preserve"> $F34 * Prices!$D33 + $G34 * Prices!$E33</f>
+        <v>0.95384615384615379</v>
       </c>
     </row>
   </sheetData>
@@ -2010,30 +2430,36 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9E8070-11EC-4D5B-882F-63D06BDC939E}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.23046875" style="7"/>
+    <col min="2" max="3" width="9.23046875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C1" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>45658</v>
       </c>
       <c r="B2" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>45659</v>
       </c>
@@ -2041,8 +2467,12 @@
         <f>B2 * Expected_Weights!E4</f>
         <v>0.95500000000000007</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C3" s="7">
+        <f>C2 * Expected_Weights!H4</f>
+        <v>0.95500000000000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
@@ -2050,8 +2480,12 @@
         <f>B3 * Expected_Weights!E5</f>
         <v>1.01</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C4" s="7">
+        <f>C3 * Expected_Weights!H5</f>
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>45661</v>
       </c>
@@ -2059,8 +2493,12 @@
         <f>B4 * Expected_Weights!E6</f>
         <v>0.96500000000000008</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C5" s="7">
+        <f>C4 * Expected_Weights!H6</f>
+        <v>0.96500000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>45662</v>
       </c>
@@ -2068,8 +2506,12 @@
         <f>B5 * Expected_Weights!E7</f>
         <v>1.0200000000000002</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C6" s="7">
+        <f>C5 * Expected_Weights!H7</f>
+        <v>1.0200000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>45663</v>
       </c>
@@ -2077,8 +2519,12 @@
         <f>B6 * Expected_Weights!E8</f>
         <v>0.97390384615384629</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C7" s="7">
+        <f>C6 * Expected_Weights!H8</f>
+        <v>0.9750000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>45664</v>
       </c>
@@ -2086,8 +2532,12 @@
         <f>B7 * Expected_Weights!E9</f>
         <v>1.0298076923076924</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C8" s="7">
+        <f>C7 * Expected_Weights!H9</f>
+        <v>1.0300000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>45665</v>
       </c>
@@ -2095,8 +2545,12 @@
         <f>B8 * Expected_Weights!E10</f>
         <v>0.98371153846153858</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C9" s="7">
+        <f>C8 * Expected_Weights!H10</f>
+        <v>0.98500000000000054</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>45666</v>
       </c>
@@ -2104,8 +2558,12 @@
         <f>B9 * Expected_Weights!E11</f>
         <v>1.0396153846153848</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C10" s="7">
+        <f>C9 * Expected_Weights!H11</f>
+        <v>1.0400000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
@@ -2113,8 +2571,12 @@
         <f>B10 * Expected_Weights!E12</f>
         <v>0.99351923076923099</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C11" s="7">
+        <f>C10 * Expected_Weights!H12</f>
+        <v>0.99500000000000044</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>45668</v>
       </c>
@@ -2122,8 +2584,12 @@
         <f>B11 * Expected_Weights!E13</f>
         <v>1.049423076923077</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C12" s="7">
+        <f>C11 * Expected_Weights!H13</f>
+        <v>1.0500000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>45669</v>
       </c>
@@ -2131,8 +2597,12 @@
         <f>B12 * Expected_Weights!E14</f>
         <v>1.0033269230769231</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C13" s="7">
+        <f>C12 * Expected_Weights!H14</f>
+        <v>1.0050000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>45670</v>
       </c>
@@ -2140,8 +2610,12 @@
         <f>B13 * Expected_Weights!E15</f>
         <v>1.0635867983367984</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C14" s="7">
+        <f>C13 * Expected_Weights!H15</f>
+        <v>1.0600000000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>45671</v>
       </c>
@@ -2149,8 +2623,12 @@
         <f>B14 * Expected_Weights!E16</f>
         <v>1.0123659043659043</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C15" s="7">
+        <f>C14 * Expected_Weights!H16</f>
+        <v>1.0150000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>45672</v>
       </c>
@@ -2158,8 +2636,12 @@
         <f>B15 * Expected_Weights!E17</f>
         <v>1.0726257796257799</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C16" s="7">
+        <f>C15 * Expected_Weights!H17</f>
+        <v>1.0700000000000005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>45673</v>
       </c>
@@ -2167,8 +2649,12 @@
         <f>B16 * Expected_Weights!E18</f>
         <v>1.0214048856548856</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C17" s="7">
+        <f>C16 * Expected_Weights!H18</f>
+        <v>1.0250000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
@@ -2176,8 +2662,12 @@
         <f>B17 * Expected_Weights!E19</f>
         <v>1.0816647609147612</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C18" s="7">
+        <f>C17 * Expected_Weights!H19</f>
+        <v>1.0800000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>45675</v>
       </c>
@@ -2185,8 +2675,12 @@
         <f>B18 * Expected_Weights!E20</f>
         <v>1.0304438669438671</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C19" s="7">
+        <f>C18 * Expected_Weights!H20</f>
+        <v>1.0350000000000008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>45676</v>
       </c>
@@ -2194,8 +2688,12 @@
         <f>B19 * Expected_Weights!E21</f>
         <v>1.0907037422037422</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C20" s="7">
+        <f>C19 * Expected_Weights!H21</f>
+        <v>1.090000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>45677</v>
       </c>
@@ -2203,8 +2701,12 @@
         <f>B20 * Expected_Weights!E22</f>
         <v>1.0407901811198421</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C21" s="7">
+        <f>C20 * Expected_Weights!H22</f>
+        <v>1.045000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>45678</v>
       </c>
@@ -2212,8 +2714,12 @@
         <f>B21 * Expected_Weights!E23</f>
         <v>1.0999469942563165</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C22" s="7">
+        <f>C21 * Expected_Weights!H23</f>
+        <v>1.1000000000000012</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>45679</v>
       </c>
@@ -2221,8 +2727,12 @@
         <f>B22 * Expected_Weights!E24</f>
         <v>1.0500334331724162</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C23" s="7">
+        <f>C22 * Expected_Weights!H24</f>
+        <v>1.055000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>45680</v>
       </c>
@@ -2230,8 +2740,12 @@
         <f>B23 * Expected_Weights!E25</f>
         <v>1.1091902463088905</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C24" s="7">
+        <f>C23 * Expected_Weights!H25</f>
+        <v>1.110000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
@@ -2239,8 +2753,12 @@
         <f>B24 * Expected_Weights!E26</f>
         <v>1.0592766852249904</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C25" s="7">
+        <f>C24 * Expected_Weights!H26</f>
+        <v>1.0650000000000008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>45682</v>
       </c>
@@ -2248,8 +2766,12 @@
         <f>B25 * Expected_Weights!E27</f>
         <v>1.1184334983614646</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C26" s="7">
+        <f>C25 * Expected_Weights!H27</f>
+        <v>1.120000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>45683</v>
       </c>
@@ -2257,8 +2779,12 @@
         <f>B26 * Expected_Weights!E28</f>
         <v>1.0685199372775644</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C27" s="7">
+        <f>C26 * Expected_Weights!H28</f>
+        <v>1.0750000000000008</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>45684</v>
       </c>
@@ -2266,8 +2792,12 @@
         <f>B27 * Expected_Weights!E29</f>
         <v>1.1321562357643171</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C28" s="7">
+        <f>C27 * Expected_Weights!H29</f>
+        <v>1.1300000000000008</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>45685</v>
       </c>
@@ -2275,8 +2805,12 @@
         <f>B28 * Expected_Weights!E30</f>
         <v>1.0770680967757849</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C29" s="7">
+        <f>C28 * Expected_Weights!H30</f>
+        <v>1.0850000000000009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>45686</v>
       </c>
@@ -2284,8 +2818,12 @@
         <f>B29 * Expected_Weights!E31</f>
         <v>1.1407043952625378</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C30" s="7">
+        <f>C29 * Expected_Weights!H31</f>
+        <v>1.140000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>45687</v>
       </c>
@@ -2293,8 +2831,12 @@
         <f>B30 * Expected_Weights!E32</f>
         <v>1.0856162562740053</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C31" s="7">
+        <f>C30 * Expected_Weights!H32</f>
+        <v>1.0950000000000009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
@@ -2302,14 +2844,22 @@
         <f>B31 * Expected_Weights!E33</f>
         <v>1.1492525547607579</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C32" s="7">
+        <f>C31 * Expected_Weights!H33</f>
+        <v>1.150000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>45689</v>
       </c>
       <c r="B33" s="7">
         <f>B32 * Expected_Weights!E34</f>
         <v>1.0941644157722259</v>
+      </c>
+      <c r="C33" s="7">
+        <f>C32 * Expected_Weights!H34</f>
+        <v>1.0969230769230778</v>
       </c>
     </row>
   </sheetData>
@@ -2319,7 +2869,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9C66B4-691D-4E6C-9B58-26BA46864B57}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.07421875" bestFit="1" customWidth="1"/>
@@ -2339,40 +2889,40 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1"/>
     </row>
@@ -2387,10 +2937,10 @@
         <v>45689</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="5">
         <v>9.42</v>
@@ -2414,7 +2964,48 @@
         <v>-4.5999999999999996</v>
       </c>
       <c r="M2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45658</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45689</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
         <v>30</v>
+      </c>
+      <c r="F3" s="5">
+        <v>9.69</v>
+      </c>
+      <c r="G3" s="5">
+        <v>197.42</v>
+      </c>
+      <c r="H3" s="5">
+        <v>75.959999999999994</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1.32</v>
+      </c>
+      <c r="J3">
+        <v>2.12</v>
+      </c>
+      <c r="K3" s="5">
+        <v>-4.62</v>
+      </c>
+      <c r="L3" s="5">
+        <v>-4.24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
